--- a/ozone/multistate/train_ozone_VTZP_MS_1_90_10_split_energies.xlsx
+++ b/ozone/multistate/train_ozone_VTZP_MS_1_90_10_split_energies.xlsx
@@ -485,7 +485,7 @@
         <v>-0.5619723753647181</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5615839958190918</v>
+        <v>-0.5613973140716553</v>
       </c>
       <c r="F2" t="n">
         <v>-225.24728984</v>
@@ -494,7 +494,7 @@
         <v>-224.6853158</v>
       </c>
       <c r="H2" t="n">
-        <v>-225.2468997958191</v>
+        <v>-225.2467131140717</v>
       </c>
     </row>
     <row r="3">
@@ -517,7 +517,7 @@
         <v>-0.5621426324215051</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5618306398391724</v>
+        <v>-0.5619345903396606</v>
       </c>
       <c r="F3" t="n">
         <v>-225.24265489</v>
@@ -526,7 +526,7 @@
         <v>-224.68051142</v>
       </c>
       <c r="H3" t="n">
-        <v>-225.2423420598392</v>
+        <v>-225.2424460103396</v>
       </c>
     </row>
     <row r="4">
@@ -549,7 +549,7 @@
         <v>-0.5708418587126228</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5711690187454224</v>
+        <v>-0.5711172819137573</v>
       </c>
       <c r="F4" t="n">
         <v>-225.18667539</v>
@@ -558,7 +558,7 @@
         <v>-224.61583209</v>
       </c>
       <c r="H4" t="n">
-        <v>-225.1870011087454</v>
+        <v>-225.1869493719138</v>
       </c>
     </row>
     <row r="5">
@@ -581,7 +581,7 @@
         <v>-0.5616664543465135</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5625271797180176</v>
+        <v>-0.5622922778129578</v>
       </c>
       <c r="F5" t="n">
         <v>-225.25610747</v>
@@ -590,7 +590,7 @@
         <v>-224.69444104</v>
       </c>
       <c r="H5" t="n">
-        <v>-225.256968219718</v>
+        <v>-225.2567333178129</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         <v>-0.561373207220107</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5620002746582031</v>
+        <v>-0.5621281266212463</v>
       </c>
       <c r="F6" t="n">
         <v>-225.26491507</v>
@@ -622,7 +622,7 @@
         <v>-224.70353832</v>
       </c>
       <c r="H6" t="n">
-        <v>-225.2655385946582</v>
+        <v>-225.2656664466213</v>
       </c>
     </row>
     <row r="7">
@@ -645,7 +645,7 @@
         <v>-0.5611652321275096</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5618654489517212</v>
+        <v>-0.5621124505996704</v>
       </c>
       <c r="F7" t="n">
         <v>-225.27170583</v>
@@ -654,7 +654,7 @@
         <v>-224.71054171</v>
       </c>
       <c r="H7" t="n">
-        <v>-225.2724071589517</v>
+        <v>-225.2726541605997</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         <v>-0.5630607581699227</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.564647912979126</v>
+        <v>-0.5647516250610352</v>
       </c>
       <c r="F8" t="n">
         <v>-225.22024666</v>
@@ -686,7 +686,7 @@
         <v>-224.6571849</v>
       </c>
       <c r="H8" t="n">
-        <v>-225.2218328129791</v>
+        <v>-225.221936525061</v>
       </c>
     </row>
     <row r="9">
@@ -709,7 +709,7 @@
         <v>-0.5777179927039896</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5789572596549988</v>
+        <v>-0.5780181884765625</v>
       </c>
       <c r="F9" t="n">
         <v>-225.15680499</v>
@@ -718,7 +718,7 @@
         <v>-224.57908425</v>
       </c>
       <c r="H9" t="n">
-        <v>-225.158041509655</v>
+        <v>-225.1571024384766</v>
       </c>
     </row>
     <row r="10">
@@ -741,7 +741,7 @@
         <v>-0.5610083271765618</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5615047216415405</v>
+        <v>-0.5614579319953918</v>
       </c>
       <c r="F10" t="n">
         <v>-225.2767779</v>
@@ -750,7 +750,7 @@
         <v>-224.71576654</v>
       </c>
       <c r="H10" t="n">
-        <v>-225.2772712616415</v>
+        <v>-225.2772244719954</v>
       </c>
     </row>
     <row r="11">
@@ -773,7 +773,7 @@
         <v>-0.5617909092313358</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5621920824050903</v>
+        <v>-0.5623974204063416</v>
       </c>
       <c r="F11" t="n">
         <v>-225.25250993</v>
@@ -782,7 +782,7 @@
         <v>-224.6907202</v>
       </c>
       <c r="H11" t="n">
-        <v>-225.2529122824051</v>
+        <v>-225.2531176204063</v>
       </c>
     </row>
     <row r="12">
@@ -805,7 +805,7 @@
         <v>-0.5621999871405967</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5627973675727844</v>
+        <v>-0.5624415874481201</v>
       </c>
       <c r="F12" t="n">
         <v>-225.2410786</v>
@@ -814,7 +814,7 @@
         <v>-224.67887615</v>
       </c>
       <c r="H12" t="n">
-        <v>-225.2416735175728</v>
+        <v>-225.2413177374481</v>
       </c>
     </row>
     <row r="13">
@@ -837,7 +837,7 @@
         <v>-0.5615063779422779</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5615005493164062</v>
+        <v>-0.5611604452133179</v>
       </c>
       <c r="F13" t="n">
         <v>-225.26095102</v>
@@ -846,7 +846,7 @@
         <v>-224.69944606</v>
       </c>
       <c r="H13" t="n">
-        <v>-225.2609466093164</v>
+        <v>-225.2606065052133</v>
       </c>
     </row>
     <row r="14">
@@ -869,7 +869,7 @@
         <v>-0.560682958101549</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5610057711601257</v>
+        <v>-0.5607841610908508</v>
       </c>
       <c r="F14" t="n">
         <v>-225.28836604</v>
@@ -878,7 +878,7 @@
         <v>-224.72768227</v>
       </c>
       <c r="H14" t="n">
-        <v>-225.2886880411601</v>
+        <v>-225.2884664310909</v>
       </c>
     </row>
     <row r="15">
@@ -901,7 +901,7 @@
         <v>-0.5606836017816704</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5605517625808716</v>
+        <v>-0.5600855350494385</v>
       </c>
       <c r="F15" t="n">
         <v>-225.29179275</v>
@@ -910,7 +910,7 @@
         <v>-224.73110986</v>
       </c>
       <c r="H15" t="n">
-        <v>-225.2916616225809</v>
+        <v>-225.2911953950494</v>
       </c>
     </row>
     <row r="16">
@@ -933,7 +933,7 @@
         <v>-0.5604517922018678</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5606651902198792</v>
+        <v>-0.560711145401001</v>
       </c>
       <c r="F16" t="n">
         <v>-225.29803666</v>
@@ -942,7 +942,7 @@
         <v>-224.73758349</v>
       </c>
       <c r="H16" t="n">
-        <v>-225.2982486802199</v>
+        <v>-225.298294635401</v>
       </c>
     </row>
     <row r="17">
@@ -965,7 +965,7 @@
         <v>-0.5604732820249573</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5610212087631226</v>
+        <v>-0.5610952377319336</v>
       </c>
       <c r="F17" t="n">
         <v>-225.29813744</v>
@@ -974,7 +974,7 @@
         <v>-224.73766292</v>
       </c>
       <c r="H17" t="n">
-        <v>-225.2986841287631</v>
+        <v>-225.2987581577319</v>
       </c>
     </row>
     <row r="18">
@@ -997,7 +997,7 @@
         <v>-0.5624192989849405</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5629222989082336</v>
+        <v>-0.5628417730331421</v>
       </c>
       <c r="F18" t="n">
         <v>-225.23544571</v>
@@ -1006,7 +1006,7 @@
         <v>-224.67302646</v>
       </c>
       <c r="H18" t="n">
-        <v>-225.2359487589082</v>
+        <v>-225.2358682330331</v>
       </c>
     </row>
     <row r="19">
@@ -1029,7 +1029,7 @@
         <v>-0.5604536184002309</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.559440553188324</v>
+        <v>-0.5598233938217163</v>
       </c>
       <c r="F19" t="n">
         <v>-225.29844495</v>
@@ -1038,7 +1038,7 @@
         <v>-224.73799238</v>
       </c>
       <c r="H19" t="n">
-        <v>-225.2974329331883</v>
+        <v>-225.2978157738217</v>
       </c>
     </row>
     <row r="20">
@@ -1061,7 +1061,7 @@
         <v>-0.5736912561319978</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5724451541900635</v>
+        <v>-0.5728176236152649</v>
       </c>
       <c r="F20" t="n">
         <v>-225.16880439</v>
@@ -1070,7 +1070,7 @@
         <v>-224.59511361</v>
       </c>
       <c r="H20" t="n">
-        <v>-225.1675587641901</v>
+        <v>-225.1679312336153</v>
       </c>
     </row>
     <row r="21">
@@ -1093,7 +1093,7 @@
         <v>-0.5632658407826493</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5628342628479004</v>
+        <v>-0.5627806782722473</v>
       </c>
       <c r="F21" t="n">
         <v>-225.21587909</v>
@@ -1102,7 +1102,7 @@
         <v>-224.65261296</v>
       </c>
       <c r="H21" t="n">
-        <v>-225.2154472228479</v>
+        <v>-225.2153936382722</v>
       </c>
     </row>
     <row r="22">
@@ -1125,7 +1125,7 @@
         <v>-0.5604550710124159</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5593727827072144</v>
+        <v>-0.5598140954971313</v>
       </c>
       <c r="F22" t="n">
         <v>-225.29845079</v>
@@ -1134,7 +1134,7 @@
         <v>-224.73799431</v>
       </c>
       <c r="H22" t="n">
-        <v>-225.2973670927072</v>
+        <v>-225.2978084054971</v>
       </c>
     </row>
     <row r="23">
@@ -1157,7 +1157,7 @@
         <v>-0.5690704114416385</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5698049068450928</v>
+        <v>-0.5701881051063538</v>
       </c>
       <c r="F23" t="n">
         <v>-225.2048981</v>
@@ -1166,7 +1166,7 @@
         <v>-224.63582966</v>
       </c>
       <c r="H23" t="n">
-        <v>-225.2056345668451</v>
+        <v>-225.2060177651064</v>
       </c>
     </row>
     <row r="24">
@@ -1189,7 +1189,7 @@
         <v>-0.5604621191776546</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.559025764465332</v>
+        <v>-0.5596584677696228</v>
       </c>
       <c r="F24" t="n">
         <v>-225.29837342</v>
@@ -1198,7 +1198,7 @@
         <v>-224.73791077</v>
       </c>
       <c r="H24" t="n">
-        <v>-225.2969365344653</v>
+        <v>-225.2975692377696</v>
       </c>
     </row>
     <row r="25">
@@ -1221,7 +1221,7 @@
         <v>-0.5605838679277613</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.559651255607605</v>
+        <v>-0.5596920251846313</v>
       </c>
       <c r="F25" t="n">
         <v>-225.29219357</v>
@@ -1230,7 +1230,7 @@
         <v>-224.73160947</v>
       </c>
       <c r="H25" t="n">
-        <v>-225.2912607256076</v>
+        <v>-225.2913014951846</v>
       </c>
     </row>
     <row r="26">
@@ -1253,7 +1253,7 @@
         <v>-0.5714756852011857</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.571315586566925</v>
+        <v>-0.5717911720275879</v>
       </c>
       <c r="F26" t="n">
         <v>-225.18168255</v>
@@ -1262,7 +1262,7 @@
         <v>-224.610209</v>
       </c>
       <c r="H26" t="n">
-        <v>-225.1815245865669</v>
+        <v>-225.1820001720276</v>
       </c>
     </row>
     <row r="27">
@@ -1285,7 +1285,7 @@
         <v>-0.571936232841328</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5711281299591064</v>
+        <v>-0.5715665817260742</v>
       </c>
       <c r="F27" t="n">
         <v>-225.17845637</v>
@@ -1294,7 +1294,7 @@
         <v>-224.60652283</v>
       </c>
       <c r="H27" t="n">
-        <v>-225.1776509599591</v>
+        <v>-225.1780894117261</v>
       </c>
     </row>
     <row r="28">
@@ -1317,7 +1317,7 @@
         <v>-0.5731034073250095</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5722545385360718</v>
+        <v>-0.5724741816520691</v>
       </c>
       <c r="F28" t="n">
         <v>-225.17161196</v>
@@ -1326,7 +1326,7 @@
         <v>-224.59850775</v>
       </c>
       <c r="H28" t="n">
-        <v>-225.1707622885361</v>
+        <v>-225.1709819316521</v>
       </c>
     </row>
     <row r="29">
@@ -1349,7 +1349,7 @@
         <v>-0.5606361824809407</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5601810812950134</v>
+        <v>-0.5601064562797546</v>
       </c>
       <c r="F29" t="n">
         <v>-225.29020784</v>
@@ -1358,7 +1358,7 @@
         <v>-224.72957273</v>
       </c>
       <c r="H29" t="n">
-        <v>-225.289753811295</v>
+        <v>-225.2896791862798</v>
       </c>
     </row>
     <row r="30">
@@ -1381,7 +1381,7 @@
         <v>-0.5604650779071859</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5594520568847656</v>
+        <v>-0.5599329471588135</v>
       </c>
       <c r="F30" t="n">
         <v>-225.29832884</v>
@@ -1390,7 +1390,7 @@
         <v>-224.73786353</v>
       </c>
       <c r="H30" t="n">
-        <v>-225.2973155868848</v>
+        <v>-225.2977964771588</v>
       </c>
     </row>
     <row r="31">
@@ -1413,7 +1413,7 @@
         <v>-0.5606092815857704</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5610653162002563</v>
+        <v>-0.5607308149337769</v>
       </c>
       <c r="F31" t="n">
         <v>-225.29123183</v>
@@ -1422,7 +1422,7 @@
         <v>-224.73062324</v>
       </c>
       <c r="H31" t="n">
-        <v>-225.2916885562003</v>
+        <v>-225.2913540549338</v>
       </c>
     </row>
     <row r="32">
@@ -1445,7 +1445,7 @@
         <v>-0.5702750029894568</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5707296133041382</v>
+        <v>-0.5704329609870911</v>
       </c>
       <c r="F32" t="n">
         <v>-225.19180153</v>
@@ -1454,7 +1454,7 @@
         <v>-224.6215263</v>
       </c>
       <c r="H32" t="n">
-        <v>-225.1922559133041</v>
+        <v>-225.1919592609871</v>
       </c>
     </row>
     <row r="33">
@@ -1477,7 +1477,7 @@
         <v>-0.561595478125881</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5619713068008423</v>
+        <v>-0.5621300935745239</v>
       </c>
       <c r="F33" t="n">
         <v>-225.25821146</v>
@@ -1486,7 +1486,7 @@
         <v>-224.69661578</v>
       </c>
       <c r="H33" t="n">
-        <v>-225.2585870868008</v>
+        <v>-225.2587458735745</v>
       </c>
     </row>
     <row r="34">
@@ -1509,7 +1509,7 @@
         <v>-0.5622605594956391</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5621137619018555</v>
+        <v>-0.5625665187835693</v>
       </c>
       <c r="F34" t="n">
         <v>-225.23948716</v>
@@ -1518,7 +1518,7 @@
         <v>-224.67722444</v>
       </c>
       <c r="H34" t="n">
-        <v>-225.2393382019019</v>
+        <v>-225.2397909587836</v>
       </c>
     </row>
     <row r="35">
@@ -1541,7 +1541,7 @@
         <v>-0.5746443121967902</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5726379156112671</v>
+        <v>-0.5731397867202759</v>
       </c>
       <c r="F35" t="n">
         <v>-225.16493294</v>
@@ -1550,7 +1550,7 @@
         <v>-224.59028469</v>
       </c>
       <c r="H35" t="n">
-        <v>-225.1629226056113</v>
+        <v>-225.1634244767203</v>
       </c>
     </row>
     <row r="36">
@@ -1573,7 +1573,7 @@
         <v>-0.561239006273508</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5622155666351318</v>
+        <v>-0.5617404580116272</v>
       </c>
       <c r="F36" t="n">
         <v>-225.26930985</v>
@@ -1582,7 +1582,7 @@
         <v>-224.70807176</v>
       </c>
       <c r="H36" t="n">
-        <v>-225.2702873266351</v>
+        <v>-225.2698122180116</v>
       </c>
     </row>
     <row r="37">
@@ -1605,7 +1605,7 @@
         <v>-0.5626895114327796</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5615082383155823</v>
+        <v>-0.5616257786750793</v>
       </c>
       <c r="F37" t="n">
         <v>-225.22880594</v>
@@ -1614,7 +1614,7 @@
         <v>-224.66611746</v>
       </c>
       <c r="H37" t="n">
-        <v>-225.2276256983156</v>
+        <v>-225.2277432386751</v>
       </c>
     </row>
     <row r="38">
@@ -1637,7 +1637,7 @@
         <v>-0.5610284875250073</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.5618078708648682</v>
+        <v>-0.5620110630989075</v>
       </c>
       <c r="F38" t="n">
         <v>-225.27623664</v>
@@ -1646,7 +1646,7 @@
         <v>-224.71520923</v>
       </c>
       <c r="H38" t="n">
-        <v>-225.2770171008649</v>
+        <v>-225.2772202930989</v>
       </c>
     </row>
     <row r="39">
@@ -1669,7 +1669,7 @@
         <v>-0.5607977838208735</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.5605403780937195</v>
+        <v>-0.5610511302947998</v>
       </c>
       <c r="F39" t="n">
         <v>-225.28419289</v>
@@ -1678,7 +1678,7 @@
         <v>-224.723395</v>
       </c>
       <c r="H39" t="n">
-        <v>-225.2839353780937</v>
+        <v>-225.2844461302948</v>
       </c>
     </row>
     <row r="40">
@@ -1701,7 +1701,7 @@
         <v>-0.5782622269891121</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.5781296491622925</v>
+        <v>-0.577136754989624</v>
       </c>
       <c r="F40" t="n">
         <v>-225.15588183</v>
@@ -1710,7 +1710,7 @@
         <v>-224.57762358</v>
       </c>
       <c r="H40" t="n">
-        <v>-225.1557532291623</v>
+        <v>-225.1547603349896</v>
       </c>
     </row>
     <row r="41">
@@ -1733,7 +1733,7 @@
         <v>-0.560536157637761</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.5599472522735596</v>
+        <v>-0.5595465302467346</v>
       </c>
       <c r="F41" t="n">
         <v>-225.29647019</v>
@@ -1742,7 +1742,7 @@
         <v>-224.735934</v>
       </c>
       <c r="H41" t="n">
-        <v>-225.2958812522735</v>
+        <v>-225.2954805302467</v>
       </c>
     </row>
     <row r="42">
@@ -1765,7 +1765,7 @@
         <v>-0.5749861304644776</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.5732817053794861</v>
+        <v>-0.5727647542953491</v>
       </c>
       <c r="F42" t="n">
         <v>-225.16374511</v>
@@ -1774,7 +1774,7 @@
         <v>-224.58875745</v>
       </c>
       <c r="H42" t="n">
-        <v>-225.1620391553795</v>
+        <v>-225.1615222042954</v>
       </c>
     </row>
     <row r="43">
@@ -1797,7 +1797,7 @@
         <v>-0.5604528957187354</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.5594327449798584</v>
+        <v>-0.5598475933074951</v>
       </c>
       <c r="F43" t="n">
         <v>-225.29845602</v>
@@ -1806,7 +1806,7 @@
         <v>-224.73800241</v>
       </c>
       <c r="H43" t="n">
-        <v>-225.2974351549799</v>
+        <v>-225.2978500033075</v>
       </c>
     </row>
     <row r="44">
@@ -1829,7 +1829,7 @@
         <v>-0.5686508746271979</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.5713759660720825</v>
+        <v>-0.5712131857872009</v>
       </c>
       <c r="F44" t="n">
         <v>-225.21015175</v>
@@ -1838,7 +1838,7 @@
         <v>-224.64150037</v>
       </c>
       <c r="H44" t="n">
-        <v>-225.2128763360721</v>
+        <v>-225.2127135557872</v>
       </c>
     </row>
     <row r="45">
@@ -1861,7 +1861,7 @@
         <v>-0.5732479011329452</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.5723379850387573</v>
+        <v>-0.5723655223846436</v>
       </c>
       <c r="F45" t="n">
         <v>-225.17089455</v>
@@ -1870,7 +1870,7 @@
         <v>-224.5976477</v>
       </c>
       <c r="H45" t="n">
-        <v>-225.1699856850388</v>
+        <v>-225.1700132223847</v>
       </c>
     </row>
     <row r="46">
@@ -1893,7 +1893,7 @@
         <v>-0.5735430243873081</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.5728045701980591</v>
+        <v>-0.57317054271698</v>
       </c>
       <c r="F46" t="n">
         <v>-225.16949051</v>
@@ -1902,7 +1902,7 @@
         <v>-224.59595025</v>
       </c>
       <c r="H46" t="n">
-        <v>-225.168754820198</v>
+        <v>-225.169120792717</v>
       </c>
     </row>
     <row r="47">
@@ -1925,7 +1925,7 @@
         <v>-0.5738405126950288</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.5739959478378296</v>
+        <v>-0.5744296312332153</v>
       </c>
       <c r="F47" t="n">
         <v>-225.16812909</v>
@@ -1934,7 +1934,7 @@
         <v>-224.59428536</v>
       </c>
       <c r="H47" t="n">
-        <v>-225.1682813078378</v>
+        <v>-225.1687149912332</v>
       </c>
     </row>
     <row r="48">
@@ -1957,7 +1957,7 @@
         <v>-0.5800822374181552</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.5791442394256592</v>
+        <v>-0.5786877274513245</v>
       </c>
       <c r="F48" t="n">
         <v>-225.15381149</v>
@@ -1966,7 +1966,7 @@
         <v>-224.57373</v>
       </c>
       <c r="H48" t="n">
-        <v>-225.1528742394257</v>
+        <v>-225.1524177274513</v>
       </c>
     </row>
     <row r="49">
@@ -1989,7 +1989,7 @@
         <v>-0.5612179277187663</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.5624412298202515</v>
+        <v>-0.5619481801986694</v>
       </c>
       <c r="F49" t="n">
         <v>-225.26991678</v>
@@ -1998,7 +1998,7 @@
         <v>-224.70869753</v>
       </c>
       <c r="H49" t="n">
-        <v>-225.2711387598202</v>
+        <v>-225.2706457101987</v>
       </c>
     </row>
     <row r="50">
@@ -2021,7 +2021,7 @@
         <v>-0.5604816866029778</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.5595479607582092</v>
+        <v>-0.5599802732467651</v>
       </c>
       <c r="F50" t="n">
         <v>-225.29785816</v>
@@ -2030,7 +2030,7 @@
         <v>-224.73737191</v>
       </c>
       <c r="H50" t="n">
-        <v>-225.2969198707582</v>
+        <v>-225.2973521832468</v>
       </c>
     </row>
     <row r="51">
@@ -2053,7 +2053,7 @@
         <v>-0.5741622187835131</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.573467493057251</v>
+        <v>-0.5740070343017578</v>
       </c>
       <c r="F51" t="n">
         <v>-225.16681358</v>
@@ -2062,7 +2062,7 @@
         <v>-224.59265598</v>
       </c>
       <c r="H51" t="n">
-        <v>-225.1661234730572</v>
+        <v>-225.1666630143017</v>
       </c>
     </row>
     <row r="52">
@@ -2085,7 +2085,7 @@
         <v>-0.5773519900515584</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5767180919647217</v>
+        <v>-0.5763300657272339</v>
       </c>
       <c r="F52" t="n">
         <v>-225.15751139</v>
@@ -2094,7 +2094,7 @@
         <v>-224.58015845</v>
       </c>
       <c r="H52" t="n">
-        <v>-225.1568765419647</v>
+        <v>-225.1564885157272</v>
       </c>
     </row>
     <row r="53">
@@ -2117,7 +2117,7 @@
         <v>-0.5612541424078498</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.562404990196228</v>
+        <v>-0.5618598461151123</v>
       </c>
       <c r="F53" t="n">
         <v>-225.26869748</v>
@@ -2126,7 +2126,7 @@
         <v>-224.7074403</v>
       </c>
       <c r="H53" t="n">
-        <v>-225.2698452901962</v>
+        <v>-225.2693001461151</v>
       </c>
     </row>
     <row r="54">
@@ -2149,7 +2149,7 @@
         <v>-0.5614828212435679</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.5612924695014954</v>
+        <v>-0.5612250566482544</v>
       </c>
       <c r="F54" t="n">
         <v>-225.26162388</v>
@@ -2158,7 +2158,7 @@
         <v>-224.7001409</v>
       </c>
       <c r="H54" t="n">
-        <v>-225.2614333695015</v>
+        <v>-225.2613659566483</v>
       </c>
     </row>
     <row r="55">
@@ -2181,7 +2181,7 @@
         <v>-0.5605293410282037</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.5602410435676575</v>
+        <v>-0.5599026679992676</v>
       </c>
       <c r="F55" t="n">
         <v>-225.29666644</v>
@@ -2190,7 +2190,7 @@
         <v>-224.73613684</v>
       </c>
       <c r="H55" t="n">
-        <v>-225.2963778835677</v>
+        <v>-225.2960395079993</v>
       </c>
     </row>
     <row r="56">
@@ -2213,7 +2213,7 @@
         <v>-0.5726926290085215</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.5701533555984497</v>
+        <v>-0.5702413320541382</v>
       </c>
       <c r="F56" t="n">
         <v>-225.17381977</v>
@@ -2222,7 +2222,7 @@
         <v>-224.60112791</v>
       </c>
       <c r="H56" t="n">
-        <v>-225.1712812655985</v>
+        <v>-225.1713692420541</v>
       </c>
     </row>
     <row r="57">
@@ -2245,7 +2245,7 @@
         <v>-0.5605570632840398</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.5599385499954224</v>
+        <v>-0.5598000288009644</v>
       </c>
       <c r="F57" t="n">
         <v>-225.29337711</v>
@@ -2254,7 +2254,7 @@
         <v>-224.73282246</v>
       </c>
       <c r="H57" t="n">
-        <v>-225.2927610099954</v>
+        <v>-225.292622488801</v>
       </c>
     </row>
     <row r="58">
@@ -2277,7 +2277,7 @@
         <v>-0.5605416338772276</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.560486912727356</v>
+        <v>-0.5602909326553345</v>
       </c>
       <c r="F58" t="n">
         <v>-225.29392578</v>
@@ -2286,7 +2286,7 @@
         <v>-224.73338452</v>
       </c>
       <c r="H58" t="n">
-        <v>-225.2938714327273</v>
+        <v>-225.2936754526553</v>
       </c>
     </row>
     <row r="59">
@@ -2309,7 +2309,7 @@
         <v>-0.5743165408360464</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5723371505737305</v>
+        <v>-0.5727325677871704</v>
       </c>
       <c r="F59" t="n">
         <v>-225.16617404</v>
@@ -2318,7 +2318,7 @@
         <v>-224.59185548</v>
       </c>
       <c r="H59" t="n">
-        <v>-225.1641926305737</v>
+        <v>-225.1645880477872</v>
       </c>
     </row>
     <row r="60">
@@ -2341,7 +2341,7 @@
         <v>-0.560469249582098</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.560059666633606</v>
+        <v>-0.560416579246521</v>
       </c>
       <c r="F60" t="n">
         <v>-225.29827453</v>
@@ -2350,7 +2350,7 @@
         <v>-224.73780628</v>
       </c>
       <c r="H60" t="n">
-        <v>-225.2978659466336</v>
+        <v>-225.2982228592465</v>
       </c>
     </row>
     <row r="61">
@@ -2373,7 +2373,7 @@
         <v>-0.560455850577817</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5610529184341431</v>
+        <v>-0.5607706308364868</v>
       </c>
       <c r="F61" t="n">
         <v>-225.29784816</v>
@@ -2382,7 +2382,7 @@
         <v>-224.73739237</v>
       </c>
       <c r="H61" t="n">
-        <v>-225.2984452884342</v>
+        <v>-225.2981630008365</v>
       </c>
     </row>
     <row r="62">
@@ -2405,7 +2405,7 @@
         <v>-0.5616388984780654</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5625209808349609</v>
+        <v>-0.5622017383575439</v>
       </c>
       <c r="F62" t="n">
         <v>-225.25681349</v>
@@ -2414,7 +2414,7 @@
         <v>-224.69517089</v>
       </c>
       <c r="H62" t="n">
-        <v>-225.257691870835</v>
+        <v>-225.2573726283576</v>
       </c>
     </row>
     <row r="63">
@@ -2437,7 +2437,7 @@
         <v>-0.5687914010152848</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.568956732749939</v>
+        <v>-0.5691063404083252</v>
       </c>
       <c r="F63" t="n">
         <v>-225.20840328</v>
@@ -2446,7 +2446,7 @@
         <v>-224.63961616</v>
       </c>
       <c r="H63" t="n">
-        <v>-225.2085728927499</v>
+        <v>-225.2087225004083</v>
       </c>
     </row>
     <row r="64">
@@ -2469,7 +2469,7 @@
         <v>-0.5629110582864231</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5641601085662842</v>
+        <v>-0.5642430186271667</v>
       </c>
       <c r="F64" t="n">
         <v>-225.22370092</v>
@@ -2478,7 +2478,7 @@
         <v>-224.6607938</v>
       </c>
       <c r="H64" t="n">
-        <v>-225.2249539085663</v>
+        <v>-225.2250368186272</v>
       </c>
     </row>
     <row r="65">
@@ -2501,7 +2501,7 @@
         <v>-0.5683885870783534</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5706777572631836</v>
+        <v>-0.5706628561019897</v>
       </c>
       <c r="F65" t="n">
         <v>-225.21363622</v>
@@ -2510,7 +2510,7 @@
         <v>-224.64524682</v>
       </c>
       <c r="H65" t="n">
-        <v>-225.2159245772632</v>
+        <v>-225.215909676102</v>
       </c>
     </row>
     <row r="66">
@@ -2533,7 +2533,7 @@
         <v>-0.5604712999631627</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5608609914779663</v>
+        <v>-0.5611129999160767</v>
       </c>
       <c r="F66" t="n">
         <v>-225.29821076</v>
@@ -2542,7 +2542,7 @@
         <v>-224.7377394</v>
       </c>
       <c r="H66" t="n">
-        <v>-225.298600391478</v>
+        <v>-225.2988523999161</v>
       </c>
     </row>
     <row r="67">
@@ -2565,7 +2565,7 @@
         <v>-0.5605193435844882</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5614425539970398</v>
+        <v>-0.5615389347076416</v>
       </c>
       <c r="F67" t="n">
         <v>-225.29469387</v>
@@ -2574,7 +2574,7 @@
         <v>-224.73417095</v>
       </c>
       <c r="H67" t="n">
-        <v>-225.295613503997</v>
+        <v>-225.2957098847076</v>
       </c>
     </row>
     <row r="68">
@@ -2597,7 +2597,7 @@
         <v>-0.561417424746826</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5621323585510254</v>
+        <v>-0.5618842244148254</v>
       </c>
       <c r="F68" t="n">
         <v>-225.26361324</v>
@@ -2606,7 +2606,7 @@
         <v>-224.70219488</v>
       </c>
       <c r="H68" t="n">
-        <v>-225.264327238551</v>
+        <v>-225.2640791044148</v>
       </c>
     </row>
     <row r="69">
@@ -2629,7 +2629,7 @@
         <v>-0.5605106006150381</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5610523223876953</v>
+        <v>-0.5609812140464783</v>
       </c>
       <c r="F69" t="n">
         <v>-225.29516883</v>
@@ -2638,7 +2638,7 @@
         <v>-224.73465701</v>
       </c>
       <c r="H69" t="n">
-        <v>-225.2957093323877</v>
+        <v>-225.2956382240465</v>
       </c>
     </row>
     <row r="70">
@@ -2661,7 +2661,7 @@
         <v>-0.5689926856250462</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.5692603588104248</v>
+        <v>-0.5692879557609558</v>
       </c>
       <c r="F70" t="n">
         <v>-225.20577499</v>
@@ -2670,7 +2670,7 @@
         <v>-224.63677833</v>
       </c>
       <c r="H70" t="n">
-        <v>-225.2060386888104</v>
+        <v>-225.206066285761</v>
       </c>
     </row>
     <row r="71">
@@ -2693,7 +2693,7 @@
         <v>-0.5605222612350288</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.560087263584137</v>
+        <v>-0.5599867105484009</v>
       </c>
       <c r="F71" t="n">
         <v>-225.29685185</v>
@@ -2702,7 +2702,7 @@
         <v>-224.73632873</v>
       </c>
       <c r="H71" t="n">
-        <v>-225.2964159935841</v>
+        <v>-225.2963154405484</v>
       </c>
     </row>
     <row r="72">
@@ -2725,7 +2725,7 @@
         <v>-0.5787646950258769</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.5795816779136658</v>
+        <v>-0.5803951025009155</v>
       </c>
       <c r="F72" t="n">
         <v>-225.15512334</v>
@@ -2734,7 +2734,7 @@
         <v>-224.57635988</v>
       </c>
       <c r="H72" t="n">
-        <v>-225.1559415579137</v>
+        <v>-225.1567549825009</v>
       </c>
     </row>
     <row r="73">
@@ -2757,7 +2757,7 @@
         <v>-0.5608487361863992</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.5606711506843567</v>
+        <v>-0.5606553554534912</v>
       </c>
       <c r="F73" t="n">
         <v>-225.2823475</v>
@@ -2766,7 +2766,7 @@
         <v>-224.72149768</v>
       </c>
       <c r="H73" t="n">
-        <v>-225.2821688306844</v>
+        <v>-225.2821530354535</v>
       </c>
     </row>
     <row r="74">
@@ -2789,7 +2789,7 @@
         <v>-0.5607624314753736</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.560404896736145</v>
+        <v>-0.560996413230896</v>
       </c>
       <c r="F74" t="n">
         <v>-225.28551178</v>
@@ -2798,7 +2798,7 @@
         <v>-224.7247505</v>
       </c>
       <c r="H74" t="n">
-        <v>-225.2851553967361</v>
+        <v>-225.2857469132309</v>
       </c>
     </row>
     <row r="75">
@@ -2821,7 +2821,7 @@
         <v>-0.560549403710723</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.5605238676071167</v>
+        <v>-0.5600166916847229</v>
       </c>
       <c r="F75" t="n">
         <v>-225.29604519</v>
@@ -2830,7 +2830,7 @@
         <v>-224.73549481</v>
       </c>
       <c r="H75" t="n">
-        <v>-225.2960186776071</v>
+        <v>-225.2955115016847</v>
       </c>
     </row>
     <row r="76">
@@ -2853,7 +2853,7 @@
         <v>-0.5701009016048719</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.5708014965057373</v>
+        <v>-0.5707686543464661</v>
       </c>
       <c r="F76" t="n">
         <v>-225.19353172</v>
@@ -2862,7 +2862,7 @@
         <v>-224.62343364</v>
       </c>
       <c r="H76" t="n">
-        <v>-225.1942351365057</v>
+        <v>-225.1942022943465</v>
       </c>
     </row>
     <row r="77">
@@ -2885,7 +2885,7 @@
         <v>-0.5626185507638157</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.5632153749465942</v>
+        <v>-0.5631239414215088</v>
       </c>
       <c r="F77" t="n">
         <v>-225.23048445</v>
@@ -2894,7 +2894,7 @@
         <v>-224.66786569</v>
       </c>
       <c r="H77" t="n">
-        <v>-225.2310810649466</v>
+        <v>-225.2309896314215</v>
       </c>
     </row>
     <row r="78">
@@ -2917,7 +2917,7 @@
         <v>-0.5605172947999156</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.5598037838935852</v>
+        <v>-0.560019850730896</v>
       </c>
       <c r="F78" t="n">
         <v>-225.2970268</v>
@@ -2926,7 +2926,7 @@
         <v>-224.73650967</v>
       </c>
       <c r="H78" t="n">
-        <v>-225.2963134538936</v>
+        <v>-225.2965295207309</v>
       </c>
     </row>
     <row r="79">
@@ -2949,7 +2949,7 @@
         <v>-0.563183469340819</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.5633100867271423</v>
+        <v>-0.5633965134620667</v>
       </c>
       <c r="F79" t="n">
         <v>-225.21763223</v>
@@ -2958,7 +2958,7 @@
         <v>-224.65444936</v>
       </c>
       <c r="H79" t="n">
-        <v>-225.2177594467271</v>
+        <v>-225.2178458734621</v>
       </c>
     </row>
     <row r="80">
@@ -2981,7 +2981,7 @@
         <v>-0.560457179594422</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.559063196182251</v>
+        <v>-0.5594508647918701</v>
       </c>
       <c r="F80" t="n">
         <v>-225.29843434</v>
@@ -2990,7 +2990,7 @@
         <v>-224.73797605</v>
       </c>
       <c r="H80" t="n">
-        <v>-225.2970392461822</v>
+        <v>-225.2974269147919</v>
       </c>
     </row>
     <row r="81">
@@ -3013,7 +3013,7 @@
         <v>-0.5604679997192124</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.5600292086601257</v>
+        <v>-0.56007981300354</v>
       </c>
       <c r="F81" t="n">
         <v>-225.29723096</v>
@@ -3022,7 +3022,7 @@
         <v>-224.73676437</v>
       </c>
       <c r="H81" t="n">
-        <v>-225.2967935786601</v>
+        <v>-225.2968441830035</v>
       </c>
     </row>
     <row r="82">
@@ -3045,7 +3045,7 @@
         <v>-0.560452385262832</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.5605756044387817</v>
+        <v>-0.5613141059875488</v>
       </c>
       <c r="F82" t="n">
         <v>-225.29839576</v>
@@ -3054,7 +3054,7 @@
         <v>-224.73794454</v>
       </c>
       <c r="H82" t="n">
-        <v>-225.2985201444388</v>
+        <v>-225.2992586459875</v>
       </c>
     </row>
     <row r="83">
@@ -3077,7 +3077,7 @@
         <v>-0.5624874309401278</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.5618607997894287</v>
+        <v>-0.5625733137130737</v>
       </c>
       <c r="F83" t="n">
         <v>-225.23380518</v>
@@ -3086,7 +3086,7 @@
         <v>-224.67132084</v>
       </c>
       <c r="H83" t="n">
-        <v>-225.2331816397894</v>
+        <v>-225.2338941537131</v>
       </c>
     </row>
     <row r="84">
@@ -3109,7 +3109,7 @@
         <v>-0.5700109548126098</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.5706932544708252</v>
+        <v>-0.5708839893341064</v>
       </c>
       <c r="F84" t="n">
         <v>-225.19439975</v>
@@ -3118,7 +3118,7 @@
         <v>-224.6243879</v>
       </c>
       <c r="H84" t="n">
-        <v>-225.1950811544708</v>
+        <v>-225.1952718893341</v>
       </c>
     </row>
     <row r="85">
@@ -3141,7 +3141,7 @@
         <v>-0.5764219721461281</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.576434850692749</v>
+        <v>-0.5756644010543823</v>
       </c>
       <c r="F85" t="n">
         <v>-225.15958396</v>
@@ -3150,7 +3150,7 @@
         <v>-224.58315862</v>
       </c>
       <c r="H85" t="n">
-        <v>-225.1595934706928</v>
+        <v>-225.1588230210544</v>
       </c>
     </row>
     <row r="86">
@@ -3173,7 +3173,7 @@
         <v>-0.570458385058267</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.5696457624435425</v>
+        <v>-0.5693793296813965</v>
       </c>
       <c r="F86" t="n">
         <v>-225.19008164</v>
@@ -3182,7 +3182,7 @@
         <v>-224.61962327</v>
       </c>
       <c r="H86" t="n">
-        <v>-225.1892690324435</v>
+        <v>-225.1890025996814</v>
       </c>
     </row>
     <row r="87">
@@ -3205,7 +3205,7 @@
         <v>-0.5694414094087012</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.5693997144699097</v>
+        <v>-0.5691353678703308</v>
       </c>
       <c r="F87" t="n">
         <v>-225.20051284</v>
@@ -3214,7 +3214,7 @@
         <v>-224.63107071</v>
       </c>
       <c r="H87" t="n">
-        <v>-225.2004704244699</v>
+        <v>-225.2002060778703</v>
       </c>
     </row>
     <row r="88">
@@ -3237,7 +3237,7 @@
         <v>-0.5607271783435397</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.5603092312812805</v>
+        <v>-0.5601434111595154</v>
       </c>
       <c r="F88" t="n">
         <v>-225.28677381</v>
@@ -3246,7 +3246,7 @@
         <v>-224.72604705</v>
       </c>
       <c r="H88" t="n">
-        <v>-225.2863562812813</v>
+        <v>-225.2861904611595</v>
       </c>
     </row>
     <row r="89">
@@ -3269,7 +3269,7 @@
         <v>-0.580028896147523</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.5785993337631226</v>
+        <v>-0.5789237022399902</v>
       </c>
       <c r="F89" t="n">
         <v>-225.15379864</v>
@@ -3278,7 +3278,7 @@
         <v>-224.57376845</v>
       </c>
       <c r="H89" t="n">
-        <v>-225.1523677837631</v>
+        <v>-225.15269215224</v>
       </c>
     </row>
     <row r="90">
@@ -3301,7 +3301,7 @@
         <v>-0.5706497316069356</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.5692869424819946</v>
+        <v>-0.569411039352417</v>
       </c>
       <c r="F90" t="n">
         <v>-225.18837211</v>
@@ -3310,7 +3310,7 @@
         <v>-224.61772466</v>
       </c>
       <c r="H90" t="n">
-        <v>-225.187011602482</v>
+        <v>-225.1871356993524</v>
       </c>
     </row>
     <row r="91">
@@ -3333,7 +3333,7 @@
         <v>-0.5607857253777176</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.5600374341011047</v>
+        <v>-0.5603359341621399</v>
       </c>
       <c r="F91" t="n">
         <v>-225.28463884</v>
@@ -3342,7 +3342,7 @@
         <v>-224.7238534</v>
       </c>
       <c r="H91" t="n">
-        <v>-225.2838908341011</v>
+        <v>-225.2841893341621</v>
       </c>
     </row>
     <row r="92">
@@ -3365,7 +3365,7 @@
         <v>-0.5717003146787518</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.5714090466499329</v>
+        <v>-0.5719629526138306</v>
       </c>
       <c r="F92" t="n">
         <v>-225.18005784</v>
@@ -3374,7 +3374,7 @@
         <v>-224.6083589</v>
       </c>
       <c r="H92" t="n">
-        <v>-225.1797679466499</v>
+        <v>-225.1803218526138</v>
       </c>
     </row>
     <row r="93">
@@ -3397,7 +3397,7 @@
         <v>-0.5618411146201703</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.5616945028305054</v>
+        <v>-0.5618904829025269</v>
       </c>
       <c r="F93" t="n">
         <v>-225.25103983</v>
@@ -3406,7 +3406,7 @@
         <v>-224.68919886</v>
       </c>
       <c r="H93" t="n">
-        <v>-225.2508933628305</v>
+        <v>-225.2510893429025</v>
       </c>
     </row>
     <row r="94">
@@ -3429,7 +3429,7 @@
         <v>-0.5713642675751729</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.5700905323028564</v>
+        <v>-0.5707101821899414</v>
       </c>
       <c r="F94" t="n">
         <v>-225.18250304</v>
@@ -3438,7 +3438,7 @@
         <v>-224.61113939</v>
       </c>
       <c r="H94" t="n">
-        <v>-225.1812299223029</v>
+        <v>-225.1818495721899</v>
       </c>
     </row>
     <row r="95">
@@ -3461,7 +3461,7 @@
         <v>-0.5607286647162497</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.561972439289093</v>
+        <v>-0.5613546371459961</v>
       </c>
       <c r="F95" t="n">
         <v>-225.29014069</v>
@@ -3470,7 +3470,7 @@
         <v>-224.72940867</v>
       </c>
       <c r="H95" t="n">
-        <v>-225.2913811092891</v>
+        <v>-225.290763307146</v>
       </c>
     </row>
     <row r="96">
@@ -3493,7 +3493,7 @@
         <v>-0.580073599239095</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.5792936086654663</v>
+        <v>-0.5787926912307739</v>
       </c>
       <c r="F96" t="n">
         <v>-225.15384901</v>
@@ -3502,7 +3502,7 @@
         <v>-224.57377734</v>
       </c>
       <c r="H96" t="n">
-        <v>-225.1530709486655</v>
+        <v>-225.1525700312308</v>
       </c>
     </row>
     <row r="97">
@@ -3525,7 +3525,7 @@
         <v>-0.5605834501432756</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.560865044593811</v>
+        <v>-0.5598835945129395</v>
       </c>
       <c r="F97" t="n">
         <v>-225.29506279</v>
@@ -3534,7 +3534,7 @@
         <v>-224.73448079</v>
       </c>
       <c r="H97" t="n">
-        <v>-225.2953458345938</v>
+        <v>-225.2943643845129</v>
       </c>
     </row>
     <row r="98">
@@ -3557,7 +3557,7 @@
         <v>-0.5611092517322197</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.5608068704605103</v>
+        <v>-0.5610339641571045</v>
       </c>
       <c r="F98" t="n">
         <v>-225.27344641</v>
@@ -3566,7 +3566,7 @@
         <v>-224.71233531</v>
       </c>
       <c r="H98" t="n">
-        <v>-225.2731421804605</v>
+        <v>-225.2733692741571</v>
       </c>
     </row>
     <row r="99">
@@ -3589,7 +3589,7 @@
         <v>-0.5604816210751256</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.5601866841316223</v>
+        <v>-0.5601431131362915</v>
       </c>
       <c r="F99" t="n">
         <v>-225.29796117</v>
@@ -3598,7 +3598,7 @@
         <v>-224.73747909</v>
       </c>
       <c r="H99" t="n">
-        <v>-225.2976657741316</v>
+        <v>-225.2976222031363</v>
       </c>
     </row>
     <row r="100">
@@ -3621,7 +3621,7 @@
         <v>-0.5689274712417925</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.5685412883758545</v>
+        <v>-0.5687986016273499</v>
       </c>
       <c r="F100" t="n">
         <v>-225.20665155</v>
@@ -3630,7 +3630,7 @@
         <v>-224.63772575</v>
       </c>
       <c r="H100" t="n">
-        <v>-225.2062670383758</v>
+        <v>-225.2065243516273</v>
       </c>
     </row>
     <row r="101">
@@ -3653,7 +3653,7 @@
         <v>-0.5610578508710259</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.5613913536071777</v>
+        <v>-0.5618023872375488</v>
       </c>
       <c r="F101" t="n">
         <v>-225.27513731</v>
@@ -3662,7 +3662,7 @@
         <v>-224.71407712</v>
       </c>
       <c r="H101" t="n">
-        <v>-225.2754684736072</v>
+        <v>-225.2758795072376</v>
       </c>
     </row>
     <row r="102">
@@ -3685,7 +3685,7 @@
         <v>-0.5605115028067326</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.5595190525054932</v>
+        <v>-0.5598738789558411</v>
       </c>
       <c r="F102" t="n">
         <v>-225.29719108</v>
@@ -3694,7 +3694,7 @@
         <v>-224.73667987</v>
       </c>
       <c r="H102" t="n">
-        <v>-225.2961989225055</v>
+        <v>-225.2965537489558</v>
       </c>
     </row>
     <row r="103">
@@ -3717,7 +3717,7 @@
         <v>-0.5687172531517235</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.5685922503471375</v>
+        <v>-0.5684181451797485</v>
       </c>
       <c r="F103" t="n">
         <v>-225.20927767</v>
@@ -3726,7 +3726,7 @@
         <v>-224.64055919</v>
       </c>
       <c r="H103" t="n">
-        <v>-225.2091514403471</v>
+        <v>-225.2089773351798</v>
       </c>
     </row>
     <row r="104">
@@ -3749,7 +3749,7 @@
         <v>-0.5720525147713127</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.5703266859054565</v>
+        <v>-0.5708025693893433</v>
       </c>
       <c r="F104" t="n">
         <v>-225.17766563</v>
@@ -3758,7 +3758,7 @@
         <v>-224.6056115</v>
       </c>
       <c r="H104" t="n">
-        <v>-225.1759381859055</v>
+        <v>-225.1764140693894</v>
       </c>
     </row>
     <row r="105">
@@ -3781,7 +3781,7 @@
         <v>-0.560966419168037</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.5603333711624146</v>
+        <v>-0.5600898861885071</v>
       </c>
       <c r="F105" t="n">
         <v>-225.27836717</v>
@@ -3790,7 +3790,7 @@
         <v>-224.71740256</v>
       </c>
       <c r="H105" t="n">
-        <v>-225.2777359311624</v>
+        <v>-225.2774924461885</v>
       </c>
     </row>
     <row r="106">
@@ -3813,7 +3813,7 @@
         <v>-0.576985398208453</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.5768267512321472</v>
+        <v>-0.576350212097168</v>
       </c>
       <c r="F106" t="n">
         <v>-225.15828899</v>
@@ -3822,7 +3822,7 @@
         <v>-224.58130537</v>
       </c>
       <c r="H106" t="n">
-        <v>-225.1581321212321</v>
+        <v>-225.1576555820972</v>
       </c>
     </row>
     <row r="107">
@@ -3845,7 +3845,7 @@
         <v>-0.5792180138243588</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.5803781747817993</v>
+        <v>-0.5808571577072144</v>
       </c>
       <c r="F107" t="n">
         <v>-225.15453286</v>
@@ -3854,7 +3854,7 @@
         <v>-224.57531238</v>
       </c>
       <c r="H107" t="n">
-        <v>-225.1556905547818</v>
+        <v>-225.1561695377072</v>
       </c>
     </row>
     <row r="108">
@@ -3877,7 +3877,7 @@
         <v>-0.5604823903721423</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.5616210699081421</v>
+        <v>-0.5621157288551331</v>
       </c>
       <c r="F108" t="n">
         <v>-225.29641099</v>
@@ -3886,7 +3886,7 @@
         <v>-224.73592775</v>
       </c>
       <c r="H108" t="n">
-        <v>-225.2975488199081</v>
+        <v>-225.2980434788551</v>
       </c>
     </row>
     <row r="109">
@@ -3909,7 +3909,7 @@
         <v>-0.5715867625071253</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.5708499550819397</v>
+        <v>-0.5715690851211548</v>
       </c>
       <c r="F109" t="n">
         <v>-225.18086739</v>
@@ -3918,7 +3918,7 @@
         <v>-224.60928218</v>
       </c>
       <c r="H109" t="n">
-        <v>-225.1801321350819</v>
+        <v>-225.1808512651212</v>
       </c>
     </row>
     <row r="110">
@@ -3941,7 +3941,7 @@
         <v>-0.5618672644468521</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.5618178844451904</v>
+        <v>-0.5619351267814636</v>
       </c>
       <c r="F110" t="n">
         <v>-225.2502982</v>
@@ -3950,7 +3950,7 @@
         <v>-224.68843119</v>
       </c>
       <c r="H110" t="n">
-        <v>-225.2502490744452</v>
+        <v>-225.2503663167815</v>
       </c>
     </row>
     <row r="111">
@@ -3973,7 +3973,7 @@
         <v>-0.5624510182144307</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.5621851682662964</v>
+        <v>-0.5625143051147461</v>
       </c>
       <c r="F111" t="n">
         <v>-225.23462704</v>
@@ -3982,7 +3982,7 @@
         <v>-224.67217541</v>
       </c>
       <c r="H111" t="n">
-        <v>-225.2343605782663</v>
+        <v>-225.2346897151147</v>
       </c>
     </row>
     <row r="112">
@@ -4005,7 +4005,7 @@
         <v>-0.5796090865527446</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.5784369111061096</v>
+        <v>-0.5792756080627441</v>
       </c>
       <c r="F112" t="n">
         <v>-225.15411244</v>
@@ -4014,7 +4014,7 @@
         <v>-224.57450532</v>
       </c>
       <c r="H112" t="n">
-        <v>-225.1529422311061</v>
+        <v>-225.1537809280627</v>
       </c>
     </row>
     <row r="113">
@@ -4037,7 +4037,7 @@
         <v>-0.5617160691764385</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.5632089972496033</v>
+        <v>-0.5632517337799072</v>
       </c>
       <c r="F113" t="n">
         <v>-225.25468199</v>
@@ -4046,7 +4046,7 @@
         <v>-224.69296704</v>
       </c>
       <c r="H113" t="n">
-        <v>-225.2561760372496</v>
+        <v>-225.2562187737799</v>
       </c>
     </row>
     <row r="114">
@@ -4069,7 +4069,7 @@
         <v>-0.5627575128186129</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.5624879598617554</v>
+        <v>-0.5629859566688538</v>
       </c>
       <c r="F114" t="n">
         <v>-225.22711512</v>
@@ -4078,7 +4078,7 @@
         <v>-224.66435553</v>
       </c>
       <c r="H114" t="n">
-        <v>-225.2268434898617</v>
+        <v>-225.2273414866688</v>
       </c>
     </row>
     <row r="115">
@@ -4101,7 +4101,7 @@
         <v>-0.5733926001943391</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.5723971128463745</v>
+        <v>-0.5723305344581604</v>
       </c>
       <c r="F115" t="n">
         <v>-225.17018731</v>
@@ -4110,7 +4110,7 @@
         <v>-224.59679513</v>
       </c>
       <c r="H115" t="n">
-        <v>-225.1691922428464</v>
+        <v>-225.1691256644582</v>
       </c>
     </row>
     <row r="116">
@@ -4133,7 +4133,7 @@
         <v>-0.5799733850909354</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.5793492794036865</v>
+        <v>-0.5795804262161255</v>
       </c>
       <c r="F116" t="n">
         <v>-225.15382173</v>
@@ -4142,7 +4142,7 @@
         <v>-224.57385059</v>
       </c>
       <c r="H116" t="n">
-        <v>-225.1531998694037</v>
+        <v>-225.1534310162161</v>
       </c>
     </row>
     <row r="117">
@@ -4165,7 +4165,7 @@
         <v>-0.5779048413354273</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.5792214870452881</v>
+        <v>-0.57802814245224</v>
       </c>
       <c r="F117" t="n">
         <v>-225.15647871</v>
@@ -4174,7 +4174,7 @@
         <v>-224.57857652</v>
       </c>
       <c r="H117" t="n">
-        <v>-225.1577980070453</v>
+        <v>-225.1566046624523</v>
       </c>
     </row>
     <row r="118">
@@ -4197,7 +4197,7 @@
         <v>-0.5605757728994951</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.5599174499511719</v>
+        <v>-0.5597944259643555</v>
       </c>
       <c r="F118" t="n">
         <v>-225.29250011</v>
@@ -4206,7 +4206,7 @@
         <v>-224.73192366</v>
       </c>
       <c r="H118" t="n">
-        <v>-225.2918411099512</v>
+        <v>-225.2917180859644</v>
       </c>
     </row>
     <row r="119">
@@ -4229,7 +4229,7 @@
         <v>-0.5789216155286447</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.5782154202461243</v>
+        <v>-0.577890157699585</v>
       </c>
       <c r="F119" t="n">
         <v>-225.15490762</v>
@@ -4238,7 +4238,7 @@
         <v>-224.57598555</v>
       </c>
       <c r="H119" t="n">
-        <v>-225.1542009702461</v>
+        <v>-225.1538757076996</v>
       </c>
     </row>
     <row r="120">
@@ -4261,7 +4261,7 @@
         <v>-0.5609988697189323</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.5604977011680603</v>
+        <v>-0.5604032278060913</v>
       </c>
       <c r="F120" t="n">
         <v>-225.27731337</v>
@@ -4270,7 +4270,7 @@
         <v>-224.71631781</v>
       </c>
       <c r="H120" t="n">
-        <v>-225.2768155111681</v>
+        <v>-225.2767210378061</v>
       </c>
     </row>
     <row r="121">
@@ -4293,7 +4293,7 @@
         <v>-0.5606086843497846</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.5608080625534058</v>
+        <v>-0.5605055093765259</v>
       </c>
       <c r="F121" t="n">
         <v>-225.29420641</v>
@@ -4302,7 +4302,7 @@
         <v>-224.73359744</v>
       </c>
       <c r="H121" t="n">
-        <v>-225.2944055025534</v>
+        <v>-225.2941029493765</v>
       </c>
     </row>
     <row r="122">
@@ -4325,7 +4325,7 @@
         <v>-0.5605015333180907</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.560731828212738</v>
+        <v>-0.5615788698196411</v>
       </c>
       <c r="F122" t="n">
         <v>-225.29561358</v>
@@ -4334,7 +4334,7 @@
         <v>-224.73511193</v>
       </c>
       <c r="H122" t="n">
-        <v>-225.2958437582127</v>
+        <v>-225.2966907998196</v>
       </c>
     </row>
     <row r="123">
@@ -4357,7 +4357,7 @@
         <v>-0.5613585715958251</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.5617396235466003</v>
+        <v>-0.5617205500602722</v>
       </c>
       <c r="F123" t="n">
         <v>-225.26555831</v>
@@ -4366,7 +4366,7 @@
         <v>-224.70420203</v>
       </c>
       <c r="H123" t="n">
-        <v>-225.2659416535466</v>
+        <v>-225.2659225800603</v>
       </c>
     </row>
     <row r="124">
@@ -4389,7 +4389,7 @@
         <v>-0.5608371928635572</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.560823380947113</v>
+        <v>-0.5607832670211792</v>
       </c>
       <c r="F124" t="n">
         <v>-225.28281801</v>
@@ -4398,7 +4398,7 @@
         <v>-224.72198151</v>
       </c>
       <c r="H124" t="n">
-        <v>-225.2828048909471</v>
+        <v>-225.2827647770212</v>
       </c>
     </row>
     <row r="125">
@@ -4421,7 +4421,7 @@
         <v>-0.5604728757416761</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.5600572824478149</v>
+        <v>-0.5600451827049255</v>
       </c>
       <c r="F125" t="n">
         <v>-225.29708298</v>
@@ -4430,7 +4430,7 @@
         <v>-224.73661356</v>
       </c>
       <c r="H125" t="n">
-        <v>-225.2966708424478</v>
+        <v>-225.2966587427049</v>
       </c>
     </row>
     <row r="126">
@@ -4453,7 +4453,7 @@
         <v>-0.5605012876083593</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.5598810315132141</v>
+        <v>-0.5600433349609375</v>
       </c>
       <c r="F126" t="n">
         <v>-225.29748874</v>
@@ -4462,7 +4462,7 @@
         <v>-224.73698836</v>
       </c>
       <c r="H126" t="n">
-        <v>-225.2968693915132</v>
+        <v>-225.2970316949609</v>
       </c>
     </row>
     <row r="127">
@@ -4485,7 +4485,7 @@
         <v>-0.5631409333637355</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.5640149116516113</v>
+        <v>-0.5641204118728638</v>
       </c>
       <c r="F127" t="n">
         <v>-225.21850569</v>
@@ -4494,7 +4494,7 @@
         <v>-224.65536365</v>
       </c>
       <c r="H127" t="n">
-        <v>-225.2193785616516</v>
+        <v>-225.2194840618729</v>
       </c>
     </row>
     <row r="128">
@@ -4517,7 +4517,7 @@
         <v>-0.572824371794403</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.5714325308799744</v>
+        <v>-0.5711355805397034</v>
       </c>
       <c r="F128" t="n">
         <v>-225.17307488</v>
@@ -4526,7 +4526,7 @@
         <v>-224.60024838</v>
       </c>
       <c r="H128" t="n">
-        <v>-225.17168091088</v>
+        <v>-225.1713839605397</v>
       </c>
     </row>
     <row r="129">
@@ -4549,7 +4549,7 @@
         <v>-0.5606438528028425</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.5608190298080444</v>
+        <v>-0.5608795881271362</v>
       </c>
       <c r="F129" t="n">
         <v>-225.28985297</v>
@@ -4558,7 +4558,7 @@
         <v>-224.72920856</v>
       </c>
       <c r="H129" t="n">
-        <v>-225.290027589808</v>
+        <v>-225.2900881481271</v>
       </c>
     </row>
     <row r="130">
@@ -4581,7 +4581,7 @@
         <v>-0.5605881812564296</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.561618447303772</v>
+        <v>-0.5608735084533691</v>
       </c>
       <c r="F130" t="n">
         <v>-225.29478881</v>
@@ -4590,7 +4590,7 @@
         <v>-224.73419811</v>
       </c>
       <c r="H130" t="n">
-        <v>-225.2958165573038</v>
+        <v>-225.2950716184534</v>
       </c>
     </row>
     <row r="131">
@@ -4613,7 +4613,7 @@
         <v>-0.5620847725390965</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.5626952648162842</v>
+        <v>-0.5619933605194092</v>
       </c>
       <c r="F131" t="n">
         <v>-225.24421573</v>
@@ -4622,7 +4622,7 @@
         <v>-224.68212996</v>
       </c>
       <c r="H131" t="n">
-        <v>-225.2448252248163</v>
+        <v>-225.2441233205194</v>
       </c>
     </row>
     <row r="132">
@@ -4645,7 +4645,7 @@
         <v>-0.5606004713385295</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.5614498853683472</v>
+        <v>-0.5608302354812622</v>
       </c>
       <c r="F132" t="n">
         <v>-225.29450344</v>
@@ -4654,7 +4654,7 @@
         <v>-224.73390383</v>
       </c>
       <c r="H132" t="n">
-        <v>-225.2953537153683</v>
+        <v>-225.2947340654813</v>
       </c>
     </row>
     <row r="133">
@@ -4677,7 +4677,7 @@
         <v>-0.5621164008843813</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.5616810321807861</v>
+        <v>-0.5620772838592529</v>
       </c>
       <c r="F133" t="n">
         <v>-225.2434373</v>
@@ -4686,7 +4686,7 @@
         <v>-224.68132281</v>
       </c>
       <c r="H133" t="n">
-        <v>-225.2430038421808</v>
+        <v>-225.2434000938593</v>
       </c>
     </row>
     <row r="134">
@@ -4709,7 +4709,7 @@
         <v>-0.5604554078462141</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.5595405697822571</v>
+        <v>-0.5600216388702393</v>
       </c>
       <c r="F134" t="n">
         <v>-225.29845799</v>
@@ -4718,7 +4718,7 @@
         <v>-224.73800309</v>
       </c>
       <c r="H134" t="n">
-        <v>-225.2975436597823</v>
+        <v>-225.2980247288702</v>
       </c>
     </row>
     <row r="135">
@@ -4741,7 +4741,7 @@
         <v>-0.5790740874543081</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.5800303816795349</v>
+        <v>-0.5804084539413452</v>
       </c>
       <c r="F135" t="n">
         <v>-225.15471078</v>
@@ -4750,7 +4750,7 @@
         <v>-224.57563611</v>
       </c>
       <c r="H135" t="n">
-        <v>-225.1556664916795</v>
+        <v>-225.1560445639414</v>
       </c>
     </row>
     <row r="136">
@@ -4773,7 +4773,7 @@
         <v>-0.5631042205455363</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.5644655227661133</v>
+        <v>-0.5645793080329895</v>
       </c>
       <c r="F136" t="n">
         <v>-225.21937723</v>
@@ -4782,7 +4782,7 @@
         <v>-224.65627556</v>
       </c>
       <c r="H136" t="n">
-        <v>-225.2207410827661</v>
+        <v>-225.220854868033</v>
       </c>
     </row>
     <row r="137">
@@ -4805,7 +4805,7 @@
         <v>-0.5629439107851546</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.5649153590202332</v>
+        <v>-0.5651635527610779</v>
       </c>
       <c r="F137" t="n">
         <v>-225.22284104</v>
@@ -4814,7 +4814,7 @@
         <v>-224.65989599</v>
       </c>
       <c r="H137" t="n">
-        <v>-225.2248113490202</v>
+        <v>-225.2250595427611</v>
       </c>
     </row>
     <row r="138">
@@ -4837,7 +4837,7 @@
         <v>-0.5622948164729811</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.5621939897537231</v>
+        <v>-0.5627353191375732</v>
       </c>
       <c r="F138" t="n">
         <v>-225.23868603</v>
@@ -4846,7 +4846,7 @@
         <v>-224.67639273</v>
       </c>
       <c r="H138" t="n">
-        <v>-225.2385867197537</v>
+        <v>-225.2391280491376</v>
       </c>
     </row>
     <row r="139">
@@ -4869,7 +4869,7 @@
         <v>-0.5692152960125743</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.5693878531455994</v>
+        <v>-0.5694522857666016</v>
       </c>
       <c r="F139" t="n">
         <v>-225.20314346</v>
@@ -4878,7 +4878,7 @@
         <v>-224.63392842</v>
       </c>
       <c r="H139" t="n">
-        <v>-225.2033162731456</v>
+        <v>-225.2033807057666</v>
       </c>
     </row>
     <row r="140">
@@ -4901,7 +4901,7 @@
         <v>-0.5618943505704344</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.5616947412490845</v>
+        <v>-0.5616483688354492</v>
       </c>
       <c r="F140" t="n">
         <v>-225.24955252</v>
@@ -4910,7 +4910,7 @@
         <v>-224.68765917</v>
       </c>
       <c r="H140" t="n">
-        <v>-225.2493539112491</v>
+        <v>-225.2493075388354</v>
       </c>
     </row>
     <row r="141">
@@ -4933,7 +4933,7 @@
         <v>-0.560534222111184</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.5607041716575623</v>
+        <v>-0.5605929493904114</v>
       </c>
       <c r="F141" t="n">
         <v>-225.29418912</v>
@@ -4942,7 +4942,7 @@
         <v>-224.7336542</v>
       </c>
       <c r="H141" t="n">
-        <v>-225.2943583716576</v>
+        <v>-225.2942471493904</v>
       </c>
     </row>
     <row r="142">
@@ -4965,7 +4965,7 @@
         <v>-0.5755171479883952</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.5765519142150879</v>
+        <v>-0.5760690569877625</v>
       </c>
       <c r="F142" t="n">
         <v>-225.16206979</v>
@@ -4974,7 +4974,7 @@
         <v>-224.58655638</v>
       </c>
       <c r="H142" t="n">
-        <v>-225.1631082942151</v>
+        <v>-225.1626254369878</v>
       </c>
     </row>
     <row r="143">
@@ -4997,7 +4997,7 @@
         <v>-0.5753385453962465</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.5756455063819885</v>
+        <v>-0.5752410292625427</v>
       </c>
       <c r="F143" t="n">
         <v>-225.16261365</v>
@@ -5006,7 +5006,7 @@
         <v>-224.58727735</v>
       </c>
       <c r="H143" t="n">
-        <v>-225.162922856382</v>
+        <v>-225.1625183792625</v>
       </c>
     </row>
     <row r="144">
@@ -5029,7 +5029,7 @@
         <v>-0.5607382335206598</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.5610906481742859</v>
+        <v>-0.5612066984176636</v>
       </c>
       <c r="F144" t="n">
         <v>-225.28635952</v>
@@ -5038,7 +5038,7 @@
         <v>-224.72562146</v>
       </c>
       <c r="H144" t="n">
-        <v>-225.2867121081743</v>
+        <v>-225.2868281584177</v>
       </c>
     </row>
     <row r="145">
@@ -5061,7 +5061,7 @@
         <v>-0.5605449770029558</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.5604091882705688</v>
+        <v>-0.5600680708885193</v>
       </c>
       <c r="F145" t="n">
         <v>-225.29626333</v>
@@ -5070,7 +5070,7 @@
         <v>-224.73572036</v>
       </c>
       <c r="H145" t="n">
-        <v>-225.2961295482706</v>
+        <v>-225.2957884308885</v>
       </c>
     </row>
     <row r="146">
@@ -5093,7 +5093,7 @@
         <v>-0.5606640512128804</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.5608437061309814</v>
+        <v>-0.5603513717651367</v>
       </c>
       <c r="F146" t="n">
         <v>-225.28912281</v>
@@ -5102,7 +5102,7 @@
         <v>-224.72845916</v>
       </c>
       <c r="H146" t="n">
-        <v>-225.289302866131</v>
+        <v>-225.2888105317651</v>
       </c>
     </row>
     <row r="147">
@@ -5125,7 +5125,7 @@
         <v>-0.5614592101875777</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.5619962215423584</v>
+        <v>-0.5618343353271484</v>
       </c>
       <c r="F147" t="n">
         <v>-225.26229205</v>
@@ -5134,7 +5134,7 @@
         <v>-224.70083088</v>
       </c>
       <c r="H147" t="n">
-        <v>-225.2628271015424</v>
+        <v>-225.2626652153272</v>
       </c>
     </row>
     <row r="148">
@@ -5157,7 +5157,7 @@
         <v>-0.5607500213750543</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.5606817007064819</v>
+        <v>-0.5610247850418091</v>
       </c>
       <c r="F148" t="n">
         <v>-225.28593882</v>
@@ -5166,7 +5166,7 @@
         <v>-224.7251893</v>
       </c>
       <c r="H148" t="n">
-        <v>-225.2858710007065</v>
+        <v>-225.2862140850418</v>
       </c>
     </row>
     <row r="149">
@@ -5189,7 +5189,7 @@
         <v>-0.5762379302233881</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.5766758322715759</v>
+        <v>-0.576088547706604</v>
       </c>
       <c r="F149" t="n">
         <v>-225.16004904</v>
@@ -5198,7 +5198,7 @@
         <v>-224.58380877</v>
       </c>
       <c r="H149" t="n">
-        <v>-225.1604846022716</v>
+        <v>-225.1598973177066</v>
       </c>
     </row>
     <row r="150">
@@ -5221,7 +5221,7 @@
         <v>-0.5630254679810178</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.5638420581817627</v>
+        <v>-0.563739538192749</v>
       </c>
       <c r="F150" t="n">
         <v>-225.22111368</v>
@@ -5230,7 +5230,7 @@
         <v>-224.65809126</v>
       </c>
       <c r="H150" t="n">
-        <v>-225.2219333181818</v>
+        <v>-225.2218307981927</v>
       </c>
     </row>
     <row r="151">
@@ -5253,7 +5253,7 @@
         <v>-0.5605676888689297</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.5610135793685913</v>
+        <v>-0.5602569580078125</v>
       </c>
       <c r="F151" t="n">
         <v>-225.29557639</v>
@@ -5262,7 +5262,7 @@
         <v>-224.73501065</v>
       </c>
       <c r="H151" t="n">
-        <v>-225.2960242293686</v>
+        <v>-225.2952676080078</v>
       </c>
     </row>
     <row r="152">
@@ -5285,7 +5285,7 @@
         <v>-0.5699252817178226</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.5707120895385742</v>
+        <v>-0.5712440013885498</v>
       </c>
       <c r="F152" t="n">
         <v>-225.19526927</v>
@@ -5294,7 +5294,7 @@
         <v>-224.62534259</v>
       </c>
       <c r="H152" t="n">
-        <v>-225.1960546795386</v>
+        <v>-225.1965865913886</v>
       </c>
     </row>
     <row r="153">
@@ -5317,7 +5317,7 @@
         <v>-0.5605574907690398</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.5611768960952759</v>
+        <v>-0.5604254007339478</v>
       </c>
       <c r="F153" t="n">
         <v>-225.29581624</v>
@@ -5326,7 +5326,7 @@
         <v>-224.73525838</v>
       </c>
       <c r="H153" t="n">
-        <v>-225.2964352760953</v>
+        <v>-225.295683780734</v>
       </c>
     </row>
     <row r="154">
@@ -5349,7 +5349,7 @@
         <v>-0.5622292647765426</v>
       </c>
       <c r="E154" t="n">
-        <v>-0.5620771050453186</v>
+        <v>-0.5624017119407654</v>
       </c>
       <c r="F154" t="n">
         <v>-225.24028476</v>
@@ -5358,7 +5358,7 @@
         <v>-224.67805238</v>
       </c>
       <c r="H154" t="n">
-        <v>-225.2401294850453</v>
+        <v>-225.2404540919408</v>
       </c>
     </row>
     <row r="155">
@@ -5381,7 +5381,7 @@
         <v>-0.5695246004416612</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.570642352104187</v>
+        <v>-0.5705198049545288</v>
       </c>
       <c r="F155" t="n">
         <v>-225.19963668</v>
@@ -5390,7 +5390,7 @@
         <v>-224.63011676</v>
       </c>
       <c r="H155" t="n">
-        <v>-225.2007591121042</v>
+        <v>-225.2006365649545</v>
       </c>
     </row>
     <row r="156">
@@ -5413,7 +5413,7 @@
         <v>-0.5606626867183757</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.5623254776000977</v>
+        <v>-0.562130331993103</v>
       </c>
       <c r="F156" t="n">
         <v>-225.29254332</v>
@@ -5422,7 +5422,7 @@
         <v>-224.73188314</v>
       </c>
       <c r="H156" t="n">
-        <v>-225.2942086176001</v>
+        <v>-225.2940134719931</v>
       </c>
     </row>
     <row r="157">
@@ -5445,7 +5445,7 @@
         <v>-0.5605028458098491</v>
       </c>
       <c r="E157" t="n">
-        <v>-0.5597230195999146</v>
+        <v>-0.560354471206665</v>
       </c>
       <c r="F157" t="n">
         <v>-225.29734507</v>
@@ -5454,7 +5454,7 @@
         <v>-224.73683928</v>
       </c>
       <c r="H157" t="n">
-        <v>-225.2965622995999</v>
+        <v>-225.2971937512067</v>
       </c>
     </row>
     <row r="158">
@@ -5477,7 +5477,7 @@
         <v>-0.5608229082450322</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.560632586479187</v>
+        <v>-0.5607274174690247</v>
       </c>
       <c r="F158" t="n">
         <v>-225.2832825</v>
@@ -5486,7 +5486,7 @@
         <v>-224.72245911</v>
       </c>
       <c r="H158" t="n">
-        <v>-225.2830916964792</v>
+        <v>-225.283186527469</v>
       </c>
     </row>
     <row r="159">
@@ -5509,7 +5509,7 @@
         <v>-0.560460498809488</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.5608342289924622</v>
+        <v>-0.5598858594894409</v>
       </c>
       <c r="F159" t="n">
         <v>-225.29750263</v>
@@ -5518,7 +5518,7 @@
         <v>-224.73704102</v>
       </c>
       <c r="H159" t="n">
-        <v>-225.2978752489925</v>
+        <v>-225.2969268794894</v>
       </c>
     </row>
     <row r="160">
@@ -5541,7 +5541,7 @@
         <v>-0.5784324775155714</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.5802799463272095</v>
+        <v>-0.5800086259841919</v>
       </c>
       <c r="F160" t="n">
         <v>-225.15561046</v>
@@ -5550,7 +5550,7 @@
         <v>-224.57717974</v>
       </c>
       <c r="H160" t="n">
-        <v>-225.1574596863272</v>
+        <v>-225.1571883659842</v>
       </c>
     </row>
     <row r="161">
@@ -5573,7 +5573,7 @@
         <v>-0.5710441377206942</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.5695317983627319</v>
+        <v>-0.5701051950454712</v>
       </c>
       <c r="F161" t="n">
         <v>-225.18499369</v>
@@ -5582,7 +5582,7 @@
         <v>-224.61394776</v>
       </c>
       <c r="H161" t="n">
-        <v>-225.1834795583627</v>
+        <v>-225.1840529550455</v>
       </c>
     </row>
     <row r="162">
@@ -5605,7 +5605,7 @@
         <v>-0.5683291223040872</v>
       </c>
       <c r="E162" t="n">
-        <v>-0.5695850849151611</v>
+        <v>-0.5698093175888062</v>
       </c>
       <c r="F162" t="n">
         <v>-225.21450376</v>
@@ -5614,7 +5614,7 @@
         <v>-224.64617854</v>
       </c>
       <c r="H162" t="n">
-        <v>-225.2157636249152</v>
+        <v>-225.2159878575888</v>
       </c>
     </row>
     <row r="163">
@@ -5637,7 +5637,7 @@
         <v>-0.561275796310949</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.5621115565299988</v>
+        <v>-0.5617706775665283</v>
       </c>
       <c r="F163" t="n">
         <v>-225.2680798</v>
@@ -5646,7 +5646,7 @@
         <v>-224.70680331</v>
       </c>
       <c r="H163" t="n">
-        <v>-225.26891486653</v>
+        <v>-225.2685739875665</v>
       </c>
     </row>
     <row r="164">
@@ -5669,7 +5669,7 @@
         <v>-0.561741051264992</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.5627909898757935</v>
+        <v>-0.5626404285430908</v>
       </c>
       <c r="F164" t="n">
         <v>-225.25396254</v>
@@ -5678,7 +5678,7 @@
         <v>-224.69222297</v>
       </c>
       <c r="H164" t="n">
-        <v>-225.2550139598758</v>
+        <v>-225.2548633985431</v>
       </c>
     </row>
     <row r="165">
@@ -5701,7 +5701,7 @@
         <v>-0.5793627507328656</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.5785006880760193</v>
+        <v>-0.5798549652099609</v>
       </c>
       <c r="F165" t="n">
         <v>-225.1543737</v>
@@ -5710,7 +5710,7 @@
         <v>-224.57501499</v>
       </c>
       <c r="H165" t="n">
-        <v>-225.153515678076</v>
+        <v>-225.15486995521</v>
       </c>
     </row>
     <row r="166">
@@ -5733,7 +5733,7 @@
         <v>-0.569601268873934</v>
       </c>
       <c r="E166" t="n">
-        <v>-0.5712951421737671</v>
+        <v>-0.5711808204650879</v>
       </c>
       <c r="F166" t="n">
         <v>-225.19876111</v>
@@ -5742,7 +5742,7 @@
         <v>-224.62916217</v>
       </c>
       <c r="H166" t="n">
-        <v>-225.2004573121738</v>
+        <v>-225.2003429904651</v>
       </c>
     </row>
     <row r="167">
@@ -5765,7 +5765,7 @@
         <v>-0.5616907528443986</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.5625271797180176</v>
+        <v>-0.5623745918273926</v>
       </c>
       <c r="F167" t="n">
         <v>-225.25539716</v>
@@ -5774,7 +5774,7 @@
         <v>-224.69370661</v>
       </c>
       <c r="H167" t="n">
-        <v>-225.256233789718</v>
+        <v>-225.2560812018274</v>
       </c>
     </row>
     <row r="168">
@@ -5797,7 +5797,7 @@
         <v>-0.5604547922124921</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.5613808631896973</v>
+        <v>-0.560886025428772</v>
       </c>
       <c r="F168" t="n">
         <v>-225.2977413</v>
@@ -5806,7 +5806,7 @@
         <v>-224.73728383</v>
       </c>
       <c r="H168" t="n">
-        <v>-225.2986646931897</v>
+        <v>-225.2981698554288</v>
       </c>
     </row>
     <row r="169">
@@ -5829,7 +5829,7 @@
         <v>-0.5608775341915639</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.5610504746437073</v>
+        <v>-0.5606286525726318</v>
       </c>
       <c r="F169" t="n">
         <v>-225.28138813</v>
@@ -5838,7 +5838,7 @@
         <v>-224.72051097</v>
       </c>
       <c r="H169" t="n">
-        <v>-225.2815614446437</v>
+        <v>-225.2811396225726</v>
       </c>
     </row>
     <row r="170">
@@ -5861,7 +5861,7 @@
         <v>-0.5608092151917555</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.5604333877563477</v>
+        <v>-0.5606094002723694</v>
       </c>
       <c r="F170" t="n">
         <v>-225.28374074</v>
@@ -5870,7 +5870,7 @@
         <v>-224.72293021</v>
       </c>
       <c r="H170" t="n">
-        <v>-225.2833635977563</v>
+        <v>-225.2835396102724</v>
       </c>
     </row>
     <row r="171">
@@ -5893,7 +5893,7 @@
         <v>-0.5604508235040235</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.5604572296142578</v>
+        <v>-0.56092369556427</v>
       </c>
       <c r="F171" t="n">
         <v>-225.29811818</v>
@@ -5902,7 +5902,7 @@
         <v>-224.73766594</v>
       </c>
       <c r="H171" t="n">
-        <v>-225.2981231696143</v>
+        <v>-225.2985896355643</v>
       </c>
     </row>
     <row r="172">
@@ -5925,7 +5925,7 @@
         <v>-0.5604960775377927</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.5612204074859619</v>
+        <v>-0.5617894530296326</v>
       </c>
       <c r="F172" t="n">
         <v>-225.29582457</v>
@@ -5934,7 +5934,7 @@
         <v>-224.73532769</v>
       </c>
       <c r="H172" t="n">
-        <v>-225.296548097486</v>
+        <v>-225.2971171430296</v>
       </c>
     </row>
     <row r="173">
@@ -5957,7 +5957,7 @@
         <v>-0.569844668116144</v>
       </c>
       <c r="E173" t="n">
-        <v>-0.5711566209793091</v>
+        <v>-0.5713517665863037</v>
       </c>
       <c r="F173" t="n">
         <v>-225.19614041</v>
@@ -5966,7 +5966,7 @@
         <v>-224.62629744</v>
       </c>
       <c r="H173" t="n">
-        <v>-225.1974540609793</v>
+        <v>-225.1976492065863</v>
       </c>
     </row>
     <row r="174">
@@ -5989,7 +5989,7 @@
         <v>-0.5724268817603142</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.5708692073822021</v>
+        <v>-0.570634126663208</v>
       </c>
       <c r="F174" t="n">
         <v>-225.17533471</v>
@@ -5998,7 +5998,7 @@
         <v>-224.6029051</v>
       </c>
       <c r="H174" t="n">
-        <v>-225.1737743073822</v>
+        <v>-225.1735392266632</v>
       </c>
     </row>
     <row r="175">
@@ -6021,7 +6021,7 @@
         <v>-0.5609355343722942</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.5612216591835022</v>
+        <v>-0.5604774951934814</v>
       </c>
       <c r="F175" t="n">
         <v>-225.27939779</v>
@@ -6030,7 +6030,7 @@
         <v>-224.71846323</v>
       </c>
       <c r="H175" t="n">
-        <v>-225.2796848891835</v>
+        <v>-225.2789407251935</v>
       </c>
     </row>
     <row r="176">
@@ -6053,7 +6053,7 @@
         <v>-0.5758777812767382</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.5763719081878662</v>
+        <v>-0.5753905773162842</v>
       </c>
       <c r="F176" t="n">
         <v>-225.16102831</v>
@@ -6062,7 +6062,7 @@
         <v>-224.58515417</v>
       </c>
       <c r="H176" t="n">
-        <v>-225.1615260781879</v>
+        <v>-225.1605447473163</v>
       </c>
     </row>
     <row r="177">
@@ -6085,7 +6085,7 @@
         <v>-0.5615293212410584</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.5613241195678711</v>
+        <v>-0.5611587762832642</v>
       </c>
       <c r="F177" t="n">
         <v>-225.26027336</v>
@@ -6094,7 +6094,7 @@
         <v>-224.6987461</v>
       </c>
       <c r="H177" t="n">
-        <v>-225.2600702195679</v>
+        <v>-225.2599048762833</v>
       </c>
     </row>
     <row r="178">
@@ -6117,7 +6117,7 @@
         <v>-0.5605270470141774</v>
       </c>
       <c r="E178" t="n">
-        <v>-0.560521125793457</v>
+        <v>-0.5607452392578125</v>
       </c>
       <c r="F178" t="n">
         <v>-225.29444521</v>
@@ -6126,7 +6126,7 @@
         <v>-224.7339164</v>
       </c>
       <c r="H178" t="n">
-        <v>-225.2944375257935</v>
+        <v>-225.2946616392578</v>
       </c>
     </row>
     <row r="179">
@@ -6149,7 +6149,7 @@
         <v>-0.5780814474039325</v>
       </c>
       <c r="E179" t="n">
-        <v>-0.5783467292785645</v>
+        <v>-0.5774295926094055</v>
       </c>
       <c r="F179" t="n">
         <v>-225.15617158</v>
@@ -6158,7 +6158,7 @@
         <v>-224.57808957</v>
       </c>
       <c r="H179" t="n">
-        <v>-225.1564362992786</v>
+        <v>-225.1555191626094</v>
       </c>
     </row>
     <row r="180">
@@ -6181,7 +6181,7 @@
         <v>-0.5739998053532331</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.5735602378845215</v>
+        <v>-0.5741154551506042</v>
       </c>
       <c r="F180" t="n">
         <v>-225.16746542</v>
@@ -6190,7 +6190,7 @@
         <v>-224.59346588</v>
       </c>
       <c r="H180" t="n">
-        <v>-225.1670261178845</v>
+        <v>-225.1675813351506</v>
       </c>
     </row>
     <row r="181">
@@ -6213,7 +6213,7 @@
         <v>-0.5688591060818556</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.568692147731781</v>
+        <v>-0.5690374970436096</v>
       </c>
       <c r="F181" t="n">
         <v>-225.20752765</v>
@@ -6222,7 +6222,7 @@
         <v>-224.63867183</v>
       </c>
       <c r="H181" t="n">
-        <v>-225.2073639777318</v>
+        <v>-225.2077093270436</v>
       </c>
     </row>
     <row r="182">
@@ -6245,7 +6245,7 @@
         <v>-0.5625166461902426</v>
       </c>
       <c r="E182" t="n">
-        <v>-0.5621657371520996</v>
+        <v>-0.5626282095909119</v>
       </c>
       <c r="F182" t="n">
         <v>-225.23297984</v>
@@ -6254,7 +6254,7 @@
         <v>-224.67046249</v>
       </c>
       <c r="H182" t="n">
-        <v>-225.2326282271521</v>
+        <v>-225.2330906995909</v>
       </c>
     </row>
     <row r="183">
@@ -6277,7 +6277,7 @@
         <v>-0.5707433558580387</v>
       </c>
       <c r="E183" t="n">
-        <v>-0.5706610679626465</v>
+        <v>-0.5705270767211914</v>
       </c>
       <c r="F183" t="n">
         <v>-225.18752193</v>
@@ -6286,7 +6286,7 @@
         <v>-224.61677735</v>
       </c>
       <c r="H183" t="n">
-        <v>-225.1874384179627</v>
+        <v>-225.1873044267212</v>
       </c>
     </row>
     <row r="184">
@@ -6309,7 +6309,7 @@
         <v>-0.5607152838402757</v>
       </c>
       <c r="E184" t="n">
-        <v>-0.5600820183753967</v>
+        <v>-0.5596016645431519</v>
       </c>
       <c r="F184" t="n">
         <v>-225.28718163</v>
@@ -6318,7 +6318,7 @@
         <v>-224.72646595</v>
       </c>
       <c r="H184" t="n">
-        <v>-225.2865479683754</v>
+        <v>-225.2860676145432</v>
       </c>
     </row>
     <row r="185">
@@ -6341,7 +6341,7 @@
         <v>-0.560616410240411</v>
       </c>
       <c r="E185" t="n">
-        <v>-0.5605553388595581</v>
+        <v>-0.5605436563491821</v>
       </c>
       <c r="F185" t="n">
         <v>-225.29089739</v>
@@ -6350,7 +6350,7 @@
         <v>-224.7302802</v>
       </c>
       <c r="H185" t="n">
-        <v>-225.2908355388596</v>
+        <v>-225.2908238563492</v>
       </c>
     </row>
     <row r="186">
@@ -6373,7 +6373,7 @@
         <v>-0.560549092035691</v>
       </c>
       <c r="E186" t="n">
-        <v>-0.5603694915771484</v>
+        <v>-0.5605124235153198</v>
       </c>
       <c r="F186" t="n">
         <v>-225.29365502</v>
@@ -6382,7 +6382,7 @@
         <v>-224.73310719</v>
       </c>
       <c r="H186" t="n">
-        <v>-225.2934766815771</v>
+        <v>-225.2936196135153</v>
       </c>
     </row>
     <row r="187">
@@ -6405,7 +6405,7 @@
         <v>-0.5799004205842048</v>
       </c>
       <c r="E187" t="n">
-        <v>-0.578727662563324</v>
+        <v>-0.5803028345108032</v>
       </c>
       <c r="F187" t="n">
         <v>-225.1538651</v>
@@ -6414,7 +6414,7 @@
         <v>-224.57396547</v>
       </c>
       <c r="H187" t="n">
-        <v>-225.1526931325633</v>
+        <v>-225.1542683045108</v>
       </c>
     </row>
     <row r="188">
@@ -6437,7 +6437,7 @@
         <v>-0.5604805348363463</v>
       </c>
       <c r="E188" t="n">
-        <v>-0.561751127243042</v>
+        <v>-0.5617527961730957</v>
       </c>
       <c r="F188" t="n">
         <v>-225.29659088</v>
@@ -6446,7 +6446,7 @@
         <v>-224.73611145</v>
       </c>
       <c r="H188" t="n">
-        <v>-225.2978625772431</v>
+        <v>-225.2978642461731</v>
       </c>
     </row>
     <row r="189">
@@ -6469,7 +6469,7 @@
         <v>-0.5607180080838016</v>
       </c>
       <c r="E189" t="n">
-        <v>-0.5613315105438232</v>
+        <v>-0.560937762260437</v>
       </c>
       <c r="F189" t="n">
         <v>-225.29057291</v>
@@ -6478,7 +6478,7 @@
         <v>-224.72985368</v>
       </c>
       <c r="H189" t="n">
-        <v>-225.2911851905438</v>
+        <v>-225.2907914422604</v>
       </c>
     </row>
     <row r="190">
@@ -6501,7 +6501,7 @@
         <v>-0.5609795021044455</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.561107873916626</v>
+        <v>-0.5609263777732849</v>
       </c>
       <c r="F190" t="n">
         <v>-225.27784311</v>
@@ -6510,7 +6510,7 @@
         <v>-224.71686314</v>
       </c>
       <c r="H190" t="n">
-        <v>-225.2779710139166</v>
+        <v>-225.2777895177733</v>
       </c>
     </row>
     <row r="191">
@@ -6533,7 +6533,7 @@
         <v>-0.5685185397374904</v>
       </c>
       <c r="E191" t="n">
-        <v>-0.5709224939346313</v>
+        <v>-0.5708856582641602</v>
       </c>
       <c r="F191" t="n">
         <v>-225.21189623</v>
@@ -6542,7 +6542,7 @@
         <v>-224.64337742</v>
       </c>
       <c r="H191" t="n">
-        <v>-225.2142999139346</v>
+        <v>-225.2142630782642</v>
       </c>
     </row>
     <row r="192">
@@ -6565,7 +6565,7 @@
         <v>-0.5609476983221717</v>
       </c>
       <c r="E192" t="n">
-        <v>-0.5602469444274902</v>
+        <v>-0.559673547744751</v>
       </c>
       <c r="F192" t="n">
         <v>-225.27888543</v>
@@ -6574,7 +6574,7 @@
         <v>-224.71793598</v>
       </c>
       <c r="H192" t="n">
-        <v>-225.2781829244275</v>
+        <v>-225.2776095277447</v>
       </c>
     </row>
     <row r="193">
@@ -6597,7 +6597,7 @@
         <v>-0.5771730440687888</v>
       </c>
       <c r="E193" t="n">
-        <v>-0.5761498212814331</v>
+        <v>-0.5756200551986694</v>
       </c>
       <c r="F193" t="n">
         <v>-225.15789216</v>
@@ -6606,7 +6606,7 @@
         <v>-224.58072215</v>
       </c>
       <c r="H193" t="n">
-        <v>-225.1568719712814</v>
+        <v>-225.1563422051987</v>
       </c>
     </row>
     <row r="194">
@@ -6629,7 +6629,7 @@
         <v>-0.5703675169648175</v>
       </c>
       <c r="E194" t="n">
-        <v>-0.5703310966491699</v>
+        <v>-0.5701597332954407</v>
       </c>
       <c r="F194" t="n">
         <v>-225.19094059</v>
@@ -6638,7 +6638,7 @@
         <v>-224.62057439</v>
       </c>
       <c r="H194" t="n">
-        <v>-225.1909054866492</v>
+        <v>-225.1907341232954</v>
       </c>
     </row>
     <row r="195">
@@ -6661,7 +6661,7 @@
         <v>-0.570184931149153</v>
       </c>
       <c r="E195" t="n">
-        <v>-0.5711162090301514</v>
+        <v>-0.5710770487785339</v>
       </c>
       <c r="F195" t="n">
         <v>-225.19266543</v>
@@ -6670,7 +6670,7 @@
         <v>-224.62247948</v>
       </c>
       <c r="H195" t="n">
-        <v>-225.1935956890302</v>
+        <v>-225.1935565287785</v>
       </c>
     </row>
     <row r="196">
@@ -6693,7 +6693,7 @@
         <v>-0.5632220574035494</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.5628519058227539</v>
+        <v>-0.5628130435943604</v>
       </c>
       <c r="F196" t="n">
         <v>-225.21675654</v>
@@ -6702,7 +6702,7 @@
         <v>-224.65353235</v>
       </c>
       <c r="H196" t="n">
-        <v>-225.2163842558228</v>
+        <v>-225.2163453935944</v>
       </c>
     </row>
     <row r="197">
@@ -6725,7 +6725,7 @@
         <v>-0.5625839625295144</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.5636035203933716</v>
+        <v>-0.5636385679244995</v>
       </c>
       <c r="F197" t="n">
         <v>-225.23131949</v>
@@ -6734,7 +6734,7 @@
         <v>-224.6687349</v>
       </c>
       <c r="H197" t="n">
-        <v>-225.2323384203934</v>
+        <v>-225.2323734679245</v>
       </c>
     </row>
     <row r="198">
@@ -6757,7 +6757,7 @@
         <v>-0.5629831489881495</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.5651277303695679</v>
+        <v>-0.5653674006462097</v>
       </c>
       <c r="F198" t="n">
         <v>-225.22197844</v>
@@ -6766,7 +6766,7 @@
         <v>-224.65899492</v>
       </c>
       <c r="H198" t="n">
-        <v>-225.2241226503696</v>
+        <v>-225.2243623206462</v>
       </c>
     </row>
     <row r="199">
@@ -6789,7 +6789,7 @@
         <v>-0.5609208647755783</v>
       </c>
       <c r="E199" t="n">
-        <v>-0.5614272356033325</v>
+        <v>-0.5611633062362671</v>
       </c>
       <c r="F199" t="n">
         <v>-225.27990419</v>
@@ -6798,7 +6798,7 @@
         <v>-224.7189843</v>
       </c>
       <c r="H199" t="n">
-        <v>-225.2804115356033</v>
+        <v>-225.2801476062363</v>
       </c>
     </row>
     <row r="200">
@@ -6821,7 +6821,7 @@
         <v>-0.5615726751466705</v>
       </c>
       <c r="E200" t="n">
-        <v>-0.5624294877052307</v>
+        <v>-0.5626032948493958</v>
       </c>
       <c r="F200" t="n">
         <v>-225.25890354</v>
@@ -6830,7 +6830,7 @@
         <v>-224.69733086</v>
       </c>
       <c r="H200" t="n">
-        <v>-225.2597603477052</v>
+        <v>-225.2599341548494</v>
       </c>
     </row>
     <row r="201">
@@ -6853,7 +6853,7 @@
         <v>-0.5607456590247469</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.5622633695602417</v>
+        <v>-0.5612376928329468</v>
       </c>
       <c r="F201" t="n">
         <v>-225.28969538</v>
@@ -6862,7 +6862,7 @@
         <v>-224.72895023</v>
       </c>
       <c r="H201" t="n">
-        <v>-225.2912135995603</v>
+        <v>-225.290187922833</v>
       </c>
     </row>
     <row r="202">
@@ -6885,7 +6885,7 @@
         <v>-0.5794898193504139</v>
       </c>
       <c r="E202" t="n">
-        <v>-0.5804072022438049</v>
+        <v>-0.5806969404220581</v>
       </c>
       <c r="F202" t="n">
         <v>-225.15423373</v>
@@ -6894,7 +6894,7 @@
         <v>-224.57474433</v>
       </c>
       <c r="H202" t="n">
-        <v>-225.1551515322438</v>
+        <v>-225.155441270422</v>
       </c>
     </row>
     <row r="203">
@@ -6917,7 +6917,7 @@
         <v>-0.5625519814581748</v>
       </c>
       <c r="E203" t="n">
-        <v>-0.5627206563949585</v>
+        <v>-0.5632253885269165</v>
       </c>
       <c r="F203" t="n">
         <v>-225.23215125</v>
@@ -6926,7 +6926,7 @@
         <v>-224.6696004</v>
       </c>
       <c r="H203" t="n">
-        <v>-225.232321056395</v>
+        <v>-225.2328257885269</v>
       </c>
     </row>
     <row r="204">
@@ -6949,7 +6949,7 @@
         <v>-0.56272243720466</v>
       </c>
       <c r="E204" t="n">
-        <v>-0.5627616047859192</v>
+        <v>-0.5630130767822266</v>
       </c>
       <c r="F204" t="n">
         <v>-225.22796201</v>
@@ -6958,7 +6958,7 @@
         <v>-224.66523823</v>
       </c>
       <c r="H204" t="n">
-        <v>-225.2279998347859</v>
+        <v>-225.2282513067822</v>
       </c>
     </row>
     <row r="205">
@@ -6981,7 +6981,7 @@
         <v>-0.5604723570352348</v>
       </c>
       <c r="E205" t="n">
-        <v>-0.5597633123397827</v>
+        <v>-0.5598905086517334</v>
       </c>
       <c r="F205" t="n">
         <v>-225.29692693</v>
@@ -6990,7 +6990,7 @@
         <v>-224.7364544</v>
       </c>
       <c r="H205" t="n">
-        <v>-225.2962177123398</v>
+        <v>-225.2963449086517</v>
       </c>
     </row>
     <row r="206">
@@ -7013,7 +7013,7 @@
         <v>-0.5605635918196767</v>
       </c>
       <c r="E206" t="n">
-        <v>-0.5596752166748047</v>
+        <v>-0.559822678565979</v>
       </c>
       <c r="F206" t="n">
         <v>-225.29309193</v>
@@ -7022,7 +7022,7 @@
         <v>-224.73253026</v>
       </c>
       <c r="H206" t="n">
-        <v>-225.2922054766748</v>
+        <v>-225.292352938566</v>
       </c>
     </row>
     <row r="207">
@@ -7045,7 +7045,7 @@
         <v>-0.5605675301347688</v>
       </c>
       <c r="E207" t="n">
-        <v>-0.55983567237854</v>
+        <v>-0.5597377419471741</v>
       </c>
       <c r="F207" t="n">
         <v>-225.29279961</v>
@@ -7054,7 +7054,7 @@
         <v>-224.73223065</v>
       </c>
       <c r="H207" t="n">
-        <v>-225.2920663223785</v>
+        <v>-225.2919683919472</v>
       </c>
     </row>
     <row r="208">
@@ -7077,7 +7077,7 @@
         <v>-0.5611821033421591</v>
       </c>
       <c r="E208" t="n">
-        <v>-0.5627718567848206</v>
+        <v>-0.5628687143325806</v>
       </c>
       <c r="F208" t="n">
         <v>-225.2711148</v>
@@ -7086,7 +7086,7 @@
         <v>-224.70993254</v>
       </c>
       <c r="H208" t="n">
-        <v>-225.2727043967848</v>
+        <v>-225.2728012543326</v>
       </c>
     </row>
     <row r="209">
@@ -7109,7 +7109,7 @@
         <v>-0.569291076088146</v>
       </c>
       <c r="E209" t="n">
-        <v>-0.5693566203117371</v>
+        <v>-0.5695001482963562</v>
       </c>
       <c r="F209" t="n">
         <v>-225.20226637</v>
@@ -7118,7 +7118,7 @@
         <v>-224.63297687</v>
       </c>
       <c r="H209" t="n">
-        <v>-225.2023334903117</v>
+        <v>-225.2024770182963</v>
       </c>
     </row>
     <row r="210">
@@ -7141,7 +7141,7 @@
         <v>-0.5606687858492168</v>
       </c>
       <c r="E210" t="n">
-        <v>-0.560738205909729</v>
+        <v>-0.5606831312179565</v>
       </c>
       <c r="F210" t="n">
         <v>-225.29217418</v>
@@ -7150,7 +7150,7 @@
         <v>-224.7315028</v>
       </c>
       <c r="H210" t="n">
-        <v>-225.2922410059097</v>
+        <v>-225.2921859312179</v>
       </c>
     </row>
     <row r="211">
@@ -7173,7 +7173,7 @@
         <v>-0.5604611180441859</v>
       </c>
       <c r="E211" t="n">
-        <v>-0.5591107606887817</v>
+        <v>-0.5594196915626526</v>
       </c>
       <c r="F211" t="n">
         <v>-225.29840858</v>
@@ -7182,7 +7182,7 @@
         <v>-224.73794822</v>
       </c>
       <c r="H211" t="n">
-        <v>-225.2970589806888</v>
+        <v>-225.2973679115626</v>
       </c>
     </row>
     <row r="212">
@@ -7205,7 +7205,7 @@
         <v>-0.5612005549317742</v>
       </c>
       <c r="E212" t="n">
-        <v>-0.5628781914710999</v>
+        <v>-0.5624465346336365</v>
       </c>
       <c r="F212" t="n">
         <v>-225.27051846</v>
@@ -7214,7 +7214,7 @@
         <v>-224.70931782</v>
       </c>
       <c r="H212" t="n">
-        <v>-225.2721960114711</v>
+        <v>-225.2717643546336</v>
       </c>
     </row>
     <row r="213">
@@ -7237,7 +7237,7 @@
         <v>-0.575158525334363</v>
       </c>
       <c r="E213" t="n">
-        <v>-0.5734868049621582</v>
+        <v>-0.5725489854812622</v>
       </c>
       <c r="F213" t="n">
         <v>-225.16317223</v>
@@ -7246,7 +7246,7 @@
         <v>-224.58801136</v>
       </c>
       <c r="H213" t="n">
-        <v>-225.1614981649622</v>
+        <v>-225.1605603454813</v>
       </c>
     </row>
     <row r="214">
@@ -7269,7 +7269,7 @@
         <v>-0.561147922343547</v>
       </c>
       <c r="E214" t="n">
-        <v>-0.560847282409668</v>
+        <v>-0.5615055561065674</v>
       </c>
       <c r="F214" t="n">
         <v>-225.27229151</v>
@@ -7278,7 +7278,7 @@
         <v>-224.7111453</v>
       </c>
       <c r="H214" t="n">
-        <v>-225.2719925824097</v>
+        <v>-225.2726508561066</v>
       </c>
     </row>
     <row r="215">
@@ -7301,7 +7301,7 @@
         <v>-0.5766159054813811</v>
       </c>
       <c r="E215" t="n">
-        <v>-0.5753872394561768</v>
+        <v>-0.5745868682861328</v>
       </c>
       <c r="F215" t="n">
         <v>-225.15913544</v>
@@ -7310,7 +7310,7 @@
         <v>-224.58252445</v>
       </c>
       <c r="H215" t="n">
-        <v>-225.1579116894562</v>
+        <v>-225.1571113182861</v>
       </c>
     </row>
     <row r="216">
@@ -7333,7 +7333,7 @@
         <v>-0.5620041082924381</v>
       </c>
       <c r="E216" t="n">
-        <v>-0.5616908073425293</v>
+        <v>-0.5618529319763184</v>
       </c>
       <c r="F216" t="n">
         <v>-225.2465275</v>
@@ -7342,7 +7342,7 @@
         <v>-224.684526</v>
       </c>
       <c r="H216" t="n">
-        <v>-225.2462168073425</v>
+        <v>-225.2463789319763</v>
       </c>
     </row>
     <row r="217">
@@ -7365,7 +7365,7 @@
         <v>-0.5604666029983394</v>
       </c>
       <c r="E217" t="n">
-        <v>-0.5608054995536804</v>
+        <v>-0.5605701208114624</v>
       </c>
       <c r="F217" t="n">
         <v>-225.29737091</v>
@@ -7374,7 +7374,7 @@
         <v>-224.73690692</v>
       </c>
       <c r="H217" t="n">
-        <v>-225.2977124195537</v>
+        <v>-225.2974770408115</v>
       </c>
     </row>
     <row r="218">
@@ -7397,7 +7397,7 @@
         <v>-0.5606973478103474</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.5604684948921204</v>
+        <v>-0.5600180625915527</v>
       </c>
       <c r="F218" t="n">
         <v>-225.29139886</v>
@@ -7406,7 +7406,7 @@
         <v>-224.73070413</v>
       </c>
       <c r="H218" t="n">
-        <v>-225.2911726248921</v>
+        <v>-225.2907221925915</v>
       </c>
     </row>
     <row r="219">
@@ -7429,7 +7429,7 @@
         <v>-0.5608918211285149</v>
       </c>
       <c r="E219" t="n">
-        <v>-0.5607122182846069</v>
+        <v>-0.5604103803634644</v>
       </c>
       <c r="F219" t="n">
         <v>-225.28089956</v>
@@ -7438,7 +7438,7 @@
         <v>-224.72000835</v>
       </c>
       <c r="H219" t="n">
-        <v>-225.2807205682846</v>
+        <v>-225.2804187303635</v>
       </c>
     </row>
     <row r="220">
@@ -7461,7 +7461,7 @@
         <v>-0.5607757601270709</v>
       </c>
       <c r="E220" t="n">
-        <v>-0.5601271390914917</v>
+        <v>-0.5603913068771362</v>
       </c>
       <c r="F220" t="n">
         <v>-225.28507851</v>
@@ -7470,7 +7470,7 @@
         <v>-224.72430525</v>
       </c>
       <c r="H220" t="n">
-        <v>-225.2844323890915</v>
+        <v>-225.2846965568771</v>
       </c>
     </row>
     <row r="221">
@@ -7493,7 +7493,7 @@
         <v>-0.5604530742197145</v>
       </c>
       <c r="E221" t="n">
-        <v>-0.5600719451904297</v>
+        <v>-0.5605454444885254</v>
       </c>
       <c r="F221" t="n">
         <v>-225.29835778</v>
@@ -7502,7 +7502,7 @@
         <v>-224.73790687</v>
       </c>
       <c r="H221" t="n">
-        <v>-225.2979788151904</v>
+        <v>-225.2984523144885</v>
       </c>
     </row>
     <row r="222">
@@ -7525,7 +7525,7 @@
         <v>-0.5607049854452557</v>
       </c>
       <c r="E222" t="n">
-        <v>-0.560507595539093</v>
+        <v>-0.5603058338165283</v>
       </c>
       <c r="F222" t="n">
         <v>-225.28758302</v>
@@ -7534,7 +7534,7 @@
         <v>-224.7268782</v>
       </c>
       <c r="H222" t="n">
-        <v>-225.2873857955391</v>
+        <v>-225.2871840338165</v>
       </c>
     </row>
     <row r="223">
@@ -7557,7 +7557,7 @@
         <v>-0.5611279302007588</v>
       </c>
       <c r="E223" t="n">
-        <v>-0.5599101781845093</v>
+        <v>-0.5600739121437073</v>
       </c>
       <c r="F223" t="n">
         <v>-225.27287156</v>
@@ -7566,7 +7566,7 @@
         <v>-224.71174302</v>
       </c>
       <c r="H223" t="n">
-        <v>-225.2716531981845</v>
+        <v>-225.2718169321437</v>
       </c>
     </row>
     <row r="224">
@@ -7589,7 +7589,7 @@
         <v>-0.5799581083291854</v>
       </c>
       <c r="E224" t="n">
-        <v>-0.5771530270576477</v>
+        <v>-0.5769917964935303</v>
       </c>
       <c r="F224" t="n">
         <v>-225.15398775</v>
@@ -7598,7 +7598,7 @@
         <v>-224.57402971</v>
       </c>
       <c r="H224" t="n">
-        <v>-225.1511827370576</v>
+        <v>-225.1510215064935</v>
       </c>
     </row>
     <row r="225">
@@ -7621,7 +7621,7 @@
         <v>-0.5697607049160757</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.5712106227874756</v>
+        <v>-0.5710905790328979</v>
       </c>
       <c r="F225" t="n">
         <v>-225.19701311</v>
@@ -7630,7 +7630,7 @@
         <v>-224.62725272</v>
       </c>
       <c r="H225" t="n">
-        <v>-225.1984633427875</v>
+        <v>-225.1983432990329</v>
       </c>
     </row>
     <row r="226">
@@ -7653,7 +7653,7 @@
         <v>-0.5619488097981822</v>
       </c>
       <c r="E226" t="n">
-        <v>-0.5619320869445801</v>
+        <v>-0.5617693662643433</v>
       </c>
       <c r="F226" t="n">
         <v>-225.2480483</v>
@@ -7662,7 +7662,7 @@
         <v>-224.68610146</v>
       </c>
       <c r="H226" t="n">
-        <v>-225.2480335469446</v>
+        <v>-225.2478708262643</v>
       </c>
     </row>
     <row r="227">
@@ -7685,7 +7685,7 @@
         <v>-0.5620289569015938</v>
       </c>
       <c r="E227" t="n">
-        <v>-0.5614206790924072</v>
+        <v>-0.5617853403091431</v>
       </c>
       <c r="F227" t="n">
         <v>-225.24576069</v>
@@ -7694,7 +7694,7 @@
         <v>-224.68373139</v>
       </c>
       <c r="H227" t="n">
-        <v>-225.2451520690924</v>
+        <v>-225.2455167303091</v>
       </c>
     </row>
     <row r="228">
@@ -7717,7 +7717,7 @@
         <v>-0.5705517783762061</v>
       </c>
       <c r="E228" t="n">
-        <v>-0.5693938136100769</v>
+        <v>-0.5693762302398682</v>
       </c>
       <c r="F228" t="n">
         <v>-225.18922522</v>
@@ -7726,7 +7726,7 @@
         <v>-224.61867311</v>
       </c>
       <c r="H228" t="n">
-        <v>-225.1880669236101</v>
+        <v>-225.1880493402399</v>
       </c>
     </row>
     <row r="229">
@@ -7749,7 +7749,7 @@
         <v>-0.5620601965621312</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.5624049305915833</v>
+        <v>-0.5622801780700684</v>
       </c>
       <c r="F229" t="n">
         <v>-225.24499009</v>
@@ -7758,7 +7758,7 @@
         <v>-224.68293269</v>
       </c>
       <c r="H229" t="n">
-        <v>-225.2453376205916</v>
+        <v>-225.2452128680701</v>
       </c>
     </row>
     <row r="230">
@@ -7781,7 +7781,7 @@
         <v>-0.5608604336038456</v>
       </c>
       <c r="E230" t="n">
-        <v>-0.5609959363937378</v>
+        <v>-0.5610067844390869</v>
       </c>
       <c r="F230" t="n">
         <v>-225.28187079</v>
@@ -7790,7 +7790,7 @@
         <v>-224.7210074</v>
       </c>
       <c r="H230" t="n">
-        <v>-225.2820033363937</v>
+        <v>-225.2820141844391</v>
       </c>
     </row>
     <row r="231">
@@ -7813,7 +7813,7 @@
         <v>-0.560453262120135</v>
       </c>
       <c r="E231" t="n">
-        <v>-0.5604740381240845</v>
+        <v>-0.5611783266067505</v>
       </c>
       <c r="F231" t="n">
         <v>-225.29819112</v>
@@ -7822,7 +7822,7 @@
         <v>-224.73773956</v>
       </c>
       <c r="H231" t="n">
-        <v>-225.2982135981241</v>
+        <v>-225.2989178866067</v>
       </c>
     </row>
     <row r="232">
@@ -7845,7 +7845,7 @@
         <v>-0.5628300392479781</v>
       </c>
       <c r="E232" t="n">
-        <v>-0.563932478427887</v>
+        <v>-0.5640819668769836</v>
       </c>
       <c r="F232" t="n">
         <v>-225.22541339</v>
@@ -7854,7 +7854,7 @@
         <v>-224.66258095</v>
       </c>
       <c r="H232" t="n">
-        <v>-225.2265134284279</v>
+        <v>-225.226662916877</v>
       </c>
     </row>
     <row r="233">
@@ -7877,7 +7877,7 @@
         <v>-0.5616207624723879</v>
       </c>
       <c r="E233" t="n">
-        <v>-0.5624866485595703</v>
+        <v>-0.5624164342880249</v>
       </c>
       <c r="F233" t="n">
         <v>-225.25751483</v>
@@ -7886,7 +7886,7 @@
         <v>-224.69589581</v>
       </c>
       <c r="H233" t="n">
-        <v>-225.2583824585596</v>
+        <v>-225.258312244288</v>
       </c>
     </row>
     <row r="234">
@@ -7909,7 +7909,7 @@
         <v>-0.5721762327777742</v>
       </c>
       <c r="E234" t="n">
-        <v>-0.57040935754776</v>
+        <v>-0.5709576010704041</v>
       </c>
       <c r="F234" t="n">
         <v>-225.1768815</v>
@@ -7918,7 +7918,7 @@
         <v>-224.60470462</v>
       </c>
       <c r="H234" t="n">
-        <v>-225.1751139775478</v>
+        <v>-225.1756622210704</v>
       </c>
     </row>
     <row r="235">
@@ -7941,7 +7941,7 @@
         <v>-0.5606284020604119</v>
       </c>
       <c r="E235" t="n">
-        <v>-0.5600534677505493</v>
+        <v>-0.5599086880683899</v>
       </c>
       <c r="F235" t="n">
         <v>-225.29055603</v>
@@ -7950,7 +7950,7 @@
         <v>-224.72992999</v>
       </c>
       <c r="H235" t="n">
-        <v>-225.2899834577505</v>
+        <v>-225.2898386780684</v>
       </c>
     </row>
     <row r="236">
@@ -7973,7 +7973,7 @@
         <v>-0.5604929171248786</v>
       </c>
       <c r="E236" t="n">
-        <v>-0.5613737106323242</v>
+        <v>-0.5618937015533447</v>
       </c>
       <c r="F236" t="n">
         <v>-225.29602772</v>
@@ -7982,7 +7982,7 @@
         <v>-224.73553614</v>
       </c>
       <c r="H236" t="n">
-        <v>-225.2969098506323</v>
+        <v>-225.2974298415533</v>
       </c>
     </row>
     <row r="237">
@@ -8005,7 +8005,7 @@
         <v>-0.5798126420202701</v>
       </c>
       <c r="E237" t="n">
-        <v>-0.5794915556907654</v>
+        <v>-0.5799721479415894</v>
       </c>
       <c r="F237" t="n">
         <v>-225.15392804</v>
@@ -8014,7 +8014,7 @@
         <v>-224.57411391</v>
       </c>
       <c r="H237" t="n">
-        <v>-225.1536054656908</v>
+        <v>-225.1540860579416</v>
       </c>
     </row>
     <row r="238">
@@ -8037,7 +8037,7 @@
         <v>-0.5756922024588516</v>
       </c>
       <c r="E238" t="n">
-        <v>-0.5772807598114014</v>
+        <v>-0.575921893119812</v>
       </c>
       <c r="F238" t="n">
         <v>-225.16154139</v>
@@ -8046,7 +8046,7 @@
         <v>-224.58584826</v>
       </c>
       <c r="H238" t="n">
-        <v>-225.1631290198114</v>
+        <v>-225.1617701531198</v>
       </c>
     </row>
     <row r="239">
@@ -8069,7 +8069,7 @@
         <v>-0.572305145531711</v>
       </c>
       <c r="E239" t="n">
-        <v>-0.5714250802993774</v>
+        <v>-0.5715011954307556</v>
       </c>
       <c r="F239" t="n">
         <v>-225.17610428</v>
@@ -8078,7 +8078,7 @@
         <v>-224.60380224</v>
       </c>
       <c r="H239" t="n">
-        <v>-225.1752273202994</v>
+        <v>-225.1753034354307</v>
       </c>
     </row>
     <row r="240">
@@ -8101,7 +8101,7 @@
         <v>-0.5609053568946925</v>
       </c>
       <c r="E240" t="n">
-        <v>-0.5608351826667786</v>
+        <v>-0.5605827569961548</v>
       </c>
       <c r="F240" t="n">
         <v>-225.28040488</v>
@@ -8110,7 +8110,7 @@
         <v>-224.71949945</v>
       </c>
       <c r="H240" t="n">
-        <v>-225.2803346326668</v>
+        <v>-225.2800822069962</v>
       </c>
     </row>
     <row r="241">
@@ -8133,7 +8133,7 @@
         <v>-0.5618158743694748</v>
       </c>
       <c r="E241" t="n">
-        <v>-0.5622025728225708</v>
+        <v>-0.5622314810752869</v>
       </c>
       <c r="F241" t="n">
         <v>-225.25177706</v>
@@ -8142,7 +8142,7 @@
         <v>-224.68996186</v>
       </c>
       <c r="H241" t="n">
-        <v>-225.2521644328226</v>
+        <v>-225.2521933410753</v>
       </c>
     </row>
     <row r="242">
@@ -8165,7 +8165,7 @@
         <v>-0.5606188441136228</v>
       </c>
       <c r="E242" t="n">
-        <v>-0.5600557327270508</v>
+        <v>-0.5594894886016846</v>
       </c>
       <c r="F242" t="n">
         <v>-225.29389776</v>
@@ -8174,7 +8174,7 @@
         <v>-224.73327914</v>
       </c>
       <c r="H242" t="n">
-        <v>-225.2933348727271</v>
+        <v>-225.2927686286017</v>
       </c>
     </row>
     <row r="243">
@@ -8197,7 +8197,7 @@
         <v>-0.5627929234369462</v>
       </c>
       <c r="E243" t="n">
-        <v>-0.5629349946975708</v>
+        <v>-0.5633278489112854</v>
       </c>
       <c r="F243" t="n">
         <v>-225.22626556</v>
@@ -8206,7 +8206,7 @@
         <v>-224.66346976</v>
       </c>
       <c r="H243" t="n">
-        <v>-225.2264047546976</v>
+        <v>-225.2267976089113</v>
       </c>
     </row>
     <row r="244">
@@ -8229,7 +8229,7 @@
         <v>-0.5606285933704219</v>
       </c>
       <c r="E244" t="n">
-        <v>-0.5598500967025757</v>
+        <v>-0.5594052076339722</v>
       </c>
       <c r="F244" t="n">
         <v>-225.29357719</v>
@@ -8238,7 +8238,7 @@
         <v>-224.73294872</v>
       </c>
       <c r="H244" t="n">
-        <v>-225.2927988167026</v>
+        <v>-225.292353927634</v>
       </c>
     </row>
     <row r="245">
@@ -8261,7 +8261,7 @@
         <v>-0.5712561080376033</v>
       </c>
       <c r="E245" t="n">
-        <v>-0.5694706439971924</v>
+        <v>-0.570137619972229</v>
       </c>
       <c r="F245" t="n">
         <v>-225.18332853</v>
@@ -8270,7 +8270,7 @@
         <v>-224.61207274</v>
       </c>
       <c r="H245" t="n">
-        <v>-225.1815433839972</v>
+        <v>-225.1822103599722</v>
       </c>
     </row>
     <row r="246">
@@ -8293,7 +8293,7 @@
         <v>-0.5760576611551641</v>
       </c>
       <c r="E246" t="n">
-        <v>-0.5771853923797607</v>
+        <v>-0.5763068199157715</v>
       </c>
       <c r="F246" t="n">
         <v>-225.16053064</v>
@@ -8302,7 +8302,7 @@
         <v>-224.58447401</v>
       </c>
       <c r="H246" t="n">
-        <v>-225.1616594023798</v>
+        <v>-225.1607808299158</v>
       </c>
     </row>
     <row r="247">
@@ -8325,7 +8325,7 @@
         <v>-0.5613371116456627</v>
       </c>
       <c r="E247" t="n">
-        <v>-0.5616456270217896</v>
+        <v>-0.5612733364105225</v>
       </c>
       <c r="F247" t="n">
         <v>-225.26619638</v>
@@ -8334,7 +8334,7 @@
         <v>-224.70486045</v>
       </c>
       <c r="H247" t="n">
-        <v>-225.2665060770218</v>
+        <v>-225.2661337864105</v>
       </c>
     </row>
     <row r="248">
@@ -8357,7 +8357,7 @@
         <v>-0.560478025514809</v>
       </c>
       <c r="E248" t="n">
-        <v>-0.5601354837417603</v>
+        <v>-0.5601140260696411</v>
       </c>
       <c r="F248" t="n">
         <v>-225.29805421</v>
@@ -8366,7 +8366,7 @@
         <v>-224.73757607</v>
       </c>
       <c r="H248" t="n">
-        <v>-225.2977115537417</v>
+        <v>-225.2976900960696</v>
       </c>
     </row>
     <row r="249">
@@ -8389,7 +8389,7 @@
         <v>-0.5800313183057491</v>
       </c>
       <c r="E249" t="n">
-        <v>-0.578052282333374</v>
+        <v>-0.5779078006744385</v>
       </c>
       <c r="F249" t="n">
         <v>-225.15390766</v>
@@ -8398,7 +8398,7 @@
         <v>-224.5738742</v>
       </c>
       <c r="H249" t="n">
-        <v>-225.1519264823334</v>
+        <v>-225.1517820006744</v>
       </c>
     </row>
     <row r="250">
@@ -8421,7 +8421,7 @@
         <v>-0.5623563274039693</v>
       </c>
       <c r="E250" t="n">
-        <v>-0.5628913640975952</v>
+        <v>-0.5635268092155457</v>
       </c>
       <c r="F250" t="n">
         <v>-225.23707295</v>
@@ -8430,7 +8430,7 @@
         <v>-224.67471739</v>
       </c>
       <c r="H250" t="n">
-        <v>-225.2376087540976</v>
+        <v>-225.2382441992156</v>
       </c>
     </row>
     <row r="251">
@@ -8453,7 +8453,7 @@
         <v>-0.5610930198979251</v>
       </c>
       <c r="E251" t="n">
-        <v>-0.5605908632278442</v>
+        <v>-0.5606828331947327</v>
       </c>
       <c r="F251" t="n">
         <v>-225.27401562</v>
@@ -8462,7 +8462,7 @@
         <v>-224.71292172</v>
       </c>
       <c r="H251" t="n">
-        <v>-225.2735125832278</v>
+        <v>-225.2736045531947</v>
       </c>
     </row>
     <row r="252">
@@ -8485,7 +8485,7 @@
         <v>-0.5614395524990284</v>
       </c>
       <c r="E252" t="n">
-        <v>-0.5619975924491882</v>
+        <v>-0.5619239807128906</v>
       </c>
       <c r="F252" t="n">
         <v>-225.26295511</v>
@@ -8494,7 +8494,7 @@
         <v>-224.70151546</v>
       </c>
       <c r="H252" t="n">
-        <v>-225.2635130524492</v>
+        <v>-225.2634394407129</v>
       </c>
     </row>
     <row r="253">
@@ -8517,7 +8517,7 @@
         <v>-0.561077798310195</v>
       </c>
       <c r="E253" t="n">
-        <v>-0.5608991980552673</v>
+        <v>-0.5611422061920166</v>
       </c>
       <c r="F253" t="n">
         <v>-225.27457912</v>
@@ -8526,7 +8526,7 @@
         <v>-224.71350218</v>
       </c>
       <c r="H253" t="n">
-        <v>-225.2744013780553</v>
+        <v>-225.274644386192</v>
       </c>
     </row>
     <row r="254">
@@ -8549,7 +8549,7 @@
         <v>-0.5767973745495261</v>
       </c>
       <c r="E254" t="n">
-        <v>-0.5759972929954529</v>
+        <v>-0.5759087800979614</v>
       </c>
       <c r="F254" t="n">
         <v>-225.15870378</v>
@@ -8558,7 +8558,7 @@
         <v>-224.58190647</v>
       </c>
       <c r="H254" t="n">
-        <v>-225.1579037629955</v>
+        <v>-225.157815250098</v>
       </c>
     </row>
     <row r="255">
@@ -8581,7 +8581,7 @@
         <v>-0.5606005481249323</v>
       </c>
       <c r="E255" t="n">
-        <v>-0.5605242848396301</v>
+        <v>-0.5607622265815735</v>
       </c>
       <c r="F255" t="n">
         <v>-225.29155939</v>
@@ -8590,7 +8590,7 @@
         <v>-224.7309592</v>
       </c>
       <c r="H255" t="n">
-        <v>-225.2914834848396</v>
+        <v>-225.2917214265816</v>
       </c>
     </row>
     <row r="256">
@@ -8613,7 +8613,7 @@
         <v>-0.5604541334277793</v>
       </c>
       <c r="E256" t="n">
-        <v>-0.5597372055053711</v>
+        <v>-0.5605045557022095</v>
       </c>
       <c r="F256" t="n">
         <v>-225.29842484</v>
@@ -8622,7 +8622,7 @@
         <v>-224.73797306</v>
       </c>
       <c r="H256" t="n">
-        <v>-225.2977102655054</v>
+        <v>-225.2984776157022</v>
       </c>
     </row>
     <row r="257">
@@ -8645,7 +8645,7 @@
         <v>-0.5606951921194305</v>
       </c>
       <c r="E257" t="n">
-        <v>-0.5615226030349731</v>
+        <v>-0.5614418983459473</v>
       </c>
       <c r="F257" t="n">
         <v>-225.28797781</v>
@@ -8654,7 +8654,7 @@
         <v>-224.72728363</v>
       </c>
       <c r="H257" t="n">
-        <v>-225.288806233035</v>
+        <v>-225.2887255283459</v>
       </c>
     </row>
     <row r="258">
@@ -8677,7 +8677,7 @@
         <v>-0.5623254321789015</v>
       </c>
       <c r="E258" t="n">
-        <v>-0.5623974800109863</v>
+        <v>-0.5626994371414185</v>
       </c>
       <c r="F258" t="n">
         <v>-225.23788123</v>
@@ -8686,7 +8686,7 @@
         <v>-224.67555694</v>
       </c>
       <c r="H258" t="n">
-        <v>-225.237954420011</v>
+        <v>-225.2382563771414</v>
       </c>
     </row>
     <row r="259">
@@ -8709,7 +8709,7 @@
         <v>-0.5718156491569193</v>
       </c>
       <c r="E259" t="n">
-        <v>-0.5715485811233521</v>
+        <v>-0.5718992352485657</v>
       </c>
       <c r="F259" t="n">
         <v>-225.17925411</v>
@@ -8718,7 +8718,7 @@
         <v>-224.60743895</v>
       </c>
       <c r="H259" t="n">
-        <v>-225.1789875311233</v>
+        <v>-225.1793381852486</v>
       </c>
     </row>
     <row r="260">
@@ -8741,7 +8741,7 @@
         <v>-0.5607582159601696</v>
       </c>
       <c r="E260" t="n">
-        <v>-0.560594379901886</v>
+        <v>-0.5596587657928467</v>
       </c>
       <c r="F260" t="n">
         <v>-225.28923695</v>
@@ -8750,7 +8750,7 @@
         <v>-224.72847849</v>
       </c>
       <c r="H260" t="n">
-        <v>-225.2890728699019</v>
+        <v>-225.2881372557928</v>
       </c>
     </row>
     <row r="261">
@@ -8773,7 +8773,7 @@
         <v>-0.5604970303069895</v>
       </c>
       <c r="E261" t="n">
-        <v>-0.5593194365501404</v>
+        <v>-0.559578537940979</v>
       </c>
       <c r="F261" t="n">
         <v>-225.29762206</v>
@@ -8782,7 +8782,7 @@
         <v>-224.73712666</v>
       </c>
       <c r="H261" t="n">
-        <v>-225.2964460965501</v>
+        <v>-225.296705197941</v>
       </c>
     </row>
     <row r="262">
@@ -8805,7 +8805,7 @@
         <v>-0.5605067203529972</v>
       </c>
       <c r="E262" t="n">
-        <v>-0.5606909394264221</v>
+        <v>-0.5605425834655762</v>
       </c>
       <c r="F262" t="n">
         <v>-225.29539504</v>
@@ -8814,7 +8814,7 @@
         <v>-224.73488843</v>
       </c>
       <c r="H262" t="n">
-        <v>-225.2955793694264</v>
+        <v>-225.2954310134656</v>
       </c>
     </row>
     <row r="263">
@@ -8837,7 +8837,7 @@
         <v>-0.5607756536712695</v>
       </c>
       <c r="E263" t="n">
-        <v>-0.5617920756340027</v>
+        <v>-0.5602918863296509</v>
       </c>
       <c r="F263" t="n">
         <v>-225.28876574</v>
@@ -8846,7 +8846,7 @@
         <v>-224.72799183</v>
       </c>
       <c r="H263" t="n">
-        <v>-225.289783905634</v>
+        <v>-225.2882837163297</v>
       </c>
     </row>
     <row r="264">
@@ -8869,7 +8869,7 @@
         <v>-0.5605195160510761</v>
       </c>
       <c r="E264" t="n">
-        <v>-0.5614949464797974</v>
+        <v>-0.5616739392280579</v>
       </c>
       <c r="F264" t="n">
         <v>-225.29493512</v>
@@ -8878,7 +8878,7 @@
         <v>-224.73441787</v>
       </c>
       <c r="H264" t="n">
-        <v>-225.2959128164798</v>
+        <v>-225.296091809228</v>
       </c>
     </row>
     <row r="265">
@@ -8901,7 +8901,7 @@
         <v>-0.5691439625219824</v>
       </c>
       <c r="E265" t="n">
-        <v>-0.5695878267288208</v>
+        <v>-0.5698561668395996</v>
       </c>
       <c r="F265" t="n">
         <v>-225.20402096</v>
@@ -8910,7 +8910,7 @@
         <v>-224.63487986</v>
       </c>
       <c r="H265" t="n">
-        <v>-225.2044676867288</v>
+        <v>-225.2047360268396</v>
       </c>
     </row>
     <row r="266">
@@ -8933,7 +8933,7 @@
         <v>-0.5621700467354463</v>
       </c>
       <c r="E266" t="n">
-        <v>-0.5623729825019836</v>
+        <v>-0.5624237060546875</v>
       </c>
       <c r="F266" t="n">
         <v>-225.24186851</v>
@@ -8942,7 +8942,7 @@
         <v>-224.67969574</v>
       </c>
       <c r="H266" t="n">
-        <v>-225.242068722502</v>
+        <v>-225.2421194460547</v>
       </c>
     </row>
     <row r="267">
@@ -8965,7 +8965,7 @@
         <v>-0.5613165956987123</v>
       </c>
       <c r="E267" t="n">
-        <v>-0.5625146627426147</v>
+        <v>-0.5622361898422241</v>
       </c>
       <c r="F267" t="n">
         <v>-225.26682945</v>
@@ -8974,7 +8974,7 @@
         <v>-224.70551355</v>
       </c>
       <c r="H267" t="n">
-        <v>-225.2680282127426</v>
+        <v>-225.2677497398422</v>
       </c>
     </row>
     <row r="268">
@@ -8997,7 +8997,7 @@
         <v>-0.5684529053410454</v>
       </c>
       <c r="E268" t="n">
-        <v>-0.5706847906112671</v>
+        <v>-0.5703800916671753</v>
       </c>
       <c r="F268" t="n">
         <v>-225.21276673</v>
@@ -9006,7 +9006,7 @@
         <v>-224.64431333</v>
       </c>
       <c r="H268" t="n">
-        <v>-225.2149981206113</v>
+        <v>-225.2146934216672</v>
       </c>
     </row>
     <row r="269">
@@ -9029,7 +9029,7 @@
         <v>-0.5800617814879363</v>
       </c>
       <c r="E269" t="n">
-        <v>-0.577551007270813</v>
+        <v>-0.5781969428062439</v>
       </c>
       <c r="F269" t="n">
         <v>-225.15379445</v>
@@ -9038,7 +9038,7 @@
         <v>-224.57373042</v>
       </c>
       <c r="H269" t="n">
-        <v>-225.1512814272708</v>
+        <v>-225.1519273628062</v>
       </c>
     </row>
     <row r="270">
@@ -9061,7 +9061,7 @@
         <v>-0.5748155319000747</v>
       </c>
       <c r="E270" t="n">
-        <v>-0.5736966729164124</v>
+        <v>-0.5736076831817627</v>
       </c>
       <c r="F270" t="n">
         <v>-225.16433211</v>
@@ -9070,7 +9070,7 @@
         <v>-224.58951531</v>
       </c>
       <c r="H270" t="n">
-        <v>-225.1632119829164</v>
+        <v>-225.1631229931818</v>
       </c>
     </row>
     <row r="271">
@@ -9093,7 +9093,7 @@
         <v>-0.5744812008905253</v>
       </c>
       <c r="E271" t="n">
-        <v>-0.572177529335022</v>
+        <v>-0.5725671052932739</v>
       </c>
       <c r="F271" t="n">
         <v>-225.16554691</v>
@@ -9102,7 +9102,7 @@
         <v>-224.59106471</v>
       </c>
       <c r="H271" t="n">
-        <v>-225.163242239335</v>
+        <v>-225.1636318152933</v>
       </c>
     </row>
     <row r="272">
@@ -9125,7 +9125,7 @@
         <v>-0.5612968333284696</v>
       </c>
       <c r="E272" t="n">
-        <v>-0.5615708827972412</v>
+        <v>-0.5612818002700806</v>
       </c>
       <c r="F272" t="n">
         <v>-225.26745727</v>
@@ -9134,7 +9134,7 @@
         <v>-224.7061612</v>
       </c>
       <c r="H272" t="n">
-        <v>-225.2677320827972</v>
+        <v>-225.2674430002701</v>
       </c>
     </row>
     <row r="273">
@@ -9157,7 +9157,7 @@
         <v>-0.5604549796581783</v>
       </c>
       <c r="E273" t="n">
-        <v>-0.5603855848312378</v>
+        <v>-0.5602787733078003</v>
       </c>
       <c r="F273" t="n">
         <v>-225.29794664</v>
@@ -9166,7 +9166,7 @@
         <v>-224.73749228</v>
       </c>
       <c r="H273" t="n">
-        <v>-225.2978778648312</v>
+        <v>-225.2977710533078</v>
       </c>
     </row>
     <row r="274">
@@ -9189,7 +9189,7 @@
         <v>-0.5604742136184562</v>
       </c>
       <c r="E274" t="n">
-        <v>-0.5605202913284302</v>
+        <v>-0.5602513551712036</v>
       </c>
       <c r="F274" t="n">
         <v>-225.29676287</v>
@@ -9198,7 +9198,7 @@
         <v>-224.73628701</v>
       </c>
       <c r="H274" t="n">
-        <v>-225.2968073013284</v>
+        <v>-225.2965383651712</v>
       </c>
     </row>
   </sheetData>
